--- a/go/pkg/mojo/geom/xlsx/test_data/example_copy.xlsx
+++ b/go/pkg/mojo/geom/xlsx/test_data/example_copy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="923">
   <si>
     <t>id</t>
   </si>
@@ -79,7 +79,7 @@
     <t>geometry</t>
   </si>
   <si>
-    <t/>
+    <t>B0FFGIO5Z1</t>
   </si>
   <si>
     <t>310115</t>
@@ -139,6 +139,9 @@
     <t>POINT (121.509333 31.174294)</t>
   </si>
   <si>
+    <t>B0FFK635YM</t>
+  </si>
+  <si>
     <t>成山路800号云顶商务广场B1层</t>
   </si>
   <si>
@@ -175,6 +178,9 @@
     <t>POINT (121.509178 31.17461)</t>
   </si>
   <si>
+    <t>B0FFJIYIMA</t>
+  </si>
+  <si>
     <t>生活服务</t>
   </si>
   <si>
@@ -211,6 +217,9 @@
     <t>POINT (121.509209 31.174823)</t>
   </si>
   <si>
+    <t>B00155L40T</t>
+  </si>
+  <si>
     <t>成山路668弄1-20、25-30号</t>
   </si>
   <si>
@@ -244,6 +253,9 @@
     <t>POINT (121.507666 31.173536)</t>
   </si>
   <si>
+    <t>B00156EMPF</t>
+  </si>
+  <si>
     <t>成山路800号云顶广场C座</t>
   </si>
   <si>
@@ -283,6 +295,9 @@
     <t>POINT (121.509001 31.174645)</t>
   </si>
   <si>
+    <t>BX10016534</t>
+  </si>
+  <si>
     <t>6号线</t>
   </si>
   <si>
@@ -319,6 +334,9 @@
     <t>POINT (121.506795 31.174496)</t>
   </si>
   <si>
+    <t>BX10026153</t>
+  </si>
+  <si>
     <t>13号线</t>
   </si>
   <si>
@@ -343,6 +361,9 @@
     <t>POINT (121.507323 31.175075)</t>
   </si>
   <si>
+    <t>BX10026150</t>
+  </si>
+  <si>
     <t>31.173056</t>
   </si>
   <si>
@@ -361,6 +382,9 @@
     <t>POINT (121.508047 31.17514)</t>
   </si>
   <si>
+    <t>BX10026151</t>
+  </si>
+  <si>
     <t>31.172597</t>
   </si>
   <si>
@@ -379,6 +403,9 @@
     <t>POINT (121.507703 31.17468)</t>
   </si>
   <si>
+    <t>BX10026152</t>
+  </si>
+  <si>
     <t>31.172689</t>
   </si>
   <si>
@@ -397,6 +424,9 @@
     <t>POINT (121.508581 31.174775)</t>
   </si>
   <si>
+    <t>B0FFIIPCWF</t>
+  </si>
+  <si>
     <t>通行设施</t>
   </si>
   <si>
@@ -430,6 +460,9 @@
     <t>POINT (121.506685 31.174455)</t>
   </si>
   <si>
+    <t>B0FFHVR5QZ</t>
+  </si>
+  <si>
     <t>6号-13号线东明路站东明路站B1</t>
   </si>
   <si>
@@ -460,6 +493,9 @@
     <t>POINT (121.508006 31.175069)</t>
   </si>
   <si>
+    <t>B0FFHRI0CR</t>
+  </si>
+  <si>
     <t>成山路668弄恒大星级公寓一期内</t>
   </si>
   <si>
@@ -496,6 +532,9 @@
     <t>POINT (121.508539 31.172247)</t>
   </si>
   <si>
+    <t>B0FFLPL973</t>
+  </si>
+  <si>
     <t>邹平路与成山路交叉口南约120米</t>
   </si>
   <si>
@@ -532,6 +571,9 @@
     <t>POINT (121.509427 31.174039)</t>
   </si>
   <si>
+    <t>B0HGP5TT3Y</t>
+  </si>
+  <si>
     <t>成山路与邹平路交叉口西南约120米</t>
   </si>
   <si>
@@ -565,6 +607,9 @@
     <t>POINT (121.508917 31.17438)</t>
   </si>
   <si>
+    <t>B00156YOLO</t>
+  </si>
+  <si>
     <t>成山路668弄-42号</t>
   </si>
   <si>
@@ -601,12 +646,18 @@
     <t>POINT (121.507378 31.172432)</t>
   </si>
   <si>
+    <t>B00155MQ12</t>
+  </si>
+  <si>
     <t>恒大居委会</t>
   </si>
   <si>
     <t>021-58801659</t>
   </si>
   <si>
+    <t>B00155LIXD</t>
+  </si>
+  <si>
     <t>31.172302</t>
   </si>
   <si>
@@ -634,6 +685,9 @@
     <t>POINT (121.506833 31.174383)</t>
   </si>
   <si>
+    <t>B0IBS7U41D</t>
+  </si>
+  <si>
     <t>成山路800号云顶大厦606室</t>
   </si>
   <si>
@@ -661,6 +715,9 @@
     <t>POINT (121.509301 31.174294)</t>
   </si>
   <si>
+    <t>B0FFG7801A</t>
+  </si>
+  <si>
     <t>31.172506</t>
   </si>
   <si>
@@ -679,6 +736,9 @@
     <t>POINT (121.509087 31.174593)</t>
   </si>
   <si>
+    <t>B0FFG77ZYC</t>
+  </si>
+  <si>
     <t>31.171914</t>
   </si>
   <si>
@@ -697,6 +757,9 @@
     <t>POINT (121.509064 31.174001)</t>
   </si>
   <si>
+    <t>B00155MQ0W</t>
+  </si>
+  <si>
     <t>31.171967</t>
   </si>
   <si>
@@ -718,6 +781,9 @@
     <t>POINT (121.509619 31.174056)</t>
   </si>
   <si>
+    <t>B00156YNX6</t>
+  </si>
+  <si>
     <t>31.171111</t>
   </si>
   <si>
@@ -748,6 +814,9 @@
     <t>POINT (121.507173 31.173193)</t>
   </si>
   <si>
+    <t>B0FFFQ1OVL</t>
+  </si>
+  <si>
     <t>成山路800号云顶广场A座1层</t>
   </si>
   <si>
@@ -784,6 +853,9 @@
     <t>POINT (121.509614 31.174108)</t>
   </si>
   <si>
+    <t>B0HBT94EHB</t>
+  </si>
+  <si>
     <t>公共设施</t>
   </si>
   <si>
@@ -814,6 +886,9 @@
     <t>POINT (121.506742 31.17435)</t>
   </si>
   <si>
+    <t>B0G2UB3G45</t>
+  </si>
+  <si>
     <t>邹平路成山路800号云顶大厦A座101室</t>
   </si>
   <si>
@@ -835,6 +910,9 @@
     <t>POINT (121.509577 31.174126)</t>
   </si>
   <si>
+    <t>BV10025902</t>
+  </si>
+  <si>
     <t>1076路;604路;782路;南川线</t>
   </si>
   <si>
@@ -868,6 +946,9 @@
     <t>POINT (121.508371 31.175032)</t>
   </si>
   <si>
+    <t>B0HGP5S2LI</t>
+  </si>
+  <si>
     <t>31.172739</t>
   </si>
   <si>
@@ -886,6 +967,9 @@
     <t>POINT (121.508813 31.174825)</t>
   </si>
   <si>
+    <t>B0FFG74QBH</t>
+  </si>
+  <si>
     <t>餐饮服务</t>
   </si>
   <si>
@@ -919,6 +1003,9 @@
     <t>POINT (121.509551 31.174388)</t>
   </si>
   <si>
+    <t>B0H32R4V3D</t>
+  </si>
+  <si>
     <t>成山路668弄2号</t>
   </si>
   <si>
@@ -949,6 +1036,9 @@
     <t>POINT (121.506698 31.174422)</t>
   </si>
   <si>
+    <t>B0FFMCU7CL</t>
+  </si>
+  <si>
     <t>86-东明路街道云顶广场a座</t>
   </si>
   <si>
@@ -970,6 +1060,9 @@
     <t>POINT (121.509434 31.174037)</t>
   </si>
   <si>
+    <t>B0FFK6V3IW</t>
+  </si>
+  <si>
     <t>成山路800号云顶国际商务12楼</t>
   </si>
   <si>
@@ -1006,6 +1099,9 @@
     <t>POINT (121.509398 31.174053)</t>
   </si>
   <si>
+    <t>B0FFJN6E2A</t>
+  </si>
+  <si>
     <t>成山路777号</t>
   </si>
   <si>
@@ -1039,6 +1135,9 @@
     <t>POINT (121.508143 31.175216)</t>
   </si>
   <si>
+    <t>B0HGP5TK46</t>
+  </si>
+  <si>
     <t>成山路800号(云顶广场)</t>
   </si>
   <si>
@@ -1069,6 +1168,9 @@
     <t>POINT (121.508955 31.173938)</t>
   </si>
   <si>
+    <t>B0HGP5U83Q</t>
+  </si>
+  <si>
     <t>邹平路与成山路交叉口西南约140米</t>
   </si>
   <si>
@@ -1099,6 +1201,9 @@
     <t>POINT (121.508964 31.173923)</t>
   </si>
   <si>
+    <t>B0H1F5EHRC</t>
+  </si>
+  <si>
     <t>邹平路185号(东明路地铁站6口向东20米)</t>
   </si>
   <si>
@@ -1129,6 +1234,9 @@
     <t>POINT (121.508036 31.174844)</t>
   </si>
   <si>
+    <t>B0GUM98VZL</t>
+  </si>
+  <si>
     <t>成山路与邹平路交叉口西南40米</t>
   </si>
   <si>
@@ -1156,6 +1264,9 @@
     <t>POINT (121.50943 31.174844)</t>
   </si>
   <si>
+    <t>B0G04B7J3X</t>
+  </si>
+  <si>
     <t>邹平路与成山路交叉口南120米</t>
   </si>
   <si>
@@ -1186,6 +1297,9 @@
     <t>POINT (121.509409 31.17403)</t>
   </si>
   <si>
+    <t>B0HGTZ964W</t>
+  </si>
+  <si>
     <t>地名地址信息</t>
   </si>
   <si>
@@ -1216,6 +1330,9 @@
     <t>POINT (121.50702 31.173603)</t>
   </si>
   <si>
+    <t>B0FFH9S1DZ</t>
+  </si>
+  <si>
     <t>成山路800号附近</t>
   </si>
   <si>
@@ -1246,6 +1363,9 @@
     <t>POINT (121.509073 31.173949)</t>
   </si>
   <si>
+    <t>B0HBGUFB9Q</t>
+  </si>
+  <si>
     <t>31.17197</t>
   </si>
   <si>
@@ -1264,6 +1384,9 @@
     <t>POINT (121.509403 31.174058)</t>
   </si>
   <si>
+    <t>B001573K69</t>
+  </si>
+  <si>
     <t>31.172592</t>
   </si>
   <si>
@@ -1291,6 +1414,9 @@
     <t>POINT (121.509342 31.17468)</t>
   </si>
   <si>
+    <t>B0FFHGIKQU</t>
+  </si>
+  <si>
     <t>成山路800号A座103室</t>
   </si>
   <si>
@@ -1324,6 +1450,9 @@
     <t>POINT (121.509613 31.174062)</t>
   </si>
   <si>
+    <t>B0FFG7TIIJ</t>
+  </si>
+  <si>
     <t>东明路1140附近</t>
   </si>
   <si>
@@ -1357,6 +1486,9 @@
     <t>POINT (121.507523 31.17199)</t>
   </si>
   <si>
+    <t>B0G1XUHOGL</t>
+  </si>
+  <si>
     <t>上海市浦东新区成山路800号云顶国际广场A幢1105</t>
   </si>
   <si>
@@ -1384,6 +1516,9 @@
     <t>POINT (121.509273 31.174039)</t>
   </si>
   <si>
+    <t>B0FFIXRVH5</t>
+  </si>
+  <si>
     <t>成山路668弄21-23号-35-58号</t>
   </si>
   <si>
@@ -1417,6 +1552,9 @@
     <t>POINT (121.508419 31.171995)</t>
   </si>
   <si>
+    <t>B0FFIXQMII</t>
+  </si>
+  <si>
     <t>31.170698</t>
   </si>
   <si>
@@ -1435,6 +1573,9 @@
     <t>POINT (121.508266 31.172784)</t>
   </si>
   <si>
+    <t>B0FFIXQ9BL</t>
+  </si>
+  <si>
     <t>31.170366</t>
   </si>
   <si>
@@ -1453,6 +1594,9 @@
     <t>POINT (121.508124 31.172451)</t>
   </si>
   <si>
+    <t>B0FFFOZEYT</t>
+  </si>
+  <si>
     <t>31.171825</t>
   </si>
   <si>
@@ -1471,6 +1615,9 @@
     <t>POINT (121.507336 31.173907)</t>
   </si>
   <si>
+    <t>B0FFINNTYS</t>
+  </si>
+  <si>
     <t>成山路804附近</t>
   </si>
   <si>
@@ -1501,6 +1648,9 @@
     <t>POINT (121.509622 31.174349)</t>
   </si>
   <si>
+    <t>B0FFIXRMR7</t>
+  </si>
+  <si>
     <t>31.169771</t>
   </si>
   <si>
@@ -1519,6 +1669,9 @@
     <t>POINT (121.508893 31.171859)</t>
   </si>
   <si>
+    <t>B0FFIXRA00</t>
+  </si>
+  <si>
     <t>31.170856</t>
   </si>
   <si>
@@ -1537,6 +1690,9 @@
     <t>POINT (121.507309 31.172939)</t>
   </si>
   <si>
+    <t>B0FFIXQTUP</t>
+  </si>
+  <si>
     <t>31.16966</t>
   </si>
   <si>
@@ -1555,6 +1711,9 @@
     <t>POINT (121.508259 31.171746)</t>
   </si>
   <si>
+    <t>B0FFIY7JJQ</t>
+  </si>
+  <si>
     <t>31.169797</t>
   </si>
   <si>
@@ -1573,6 +1732,9 @@
     <t>POINT (121.509093 31.171886)</t>
   </si>
   <si>
+    <t>B0FFIXRO4Z</t>
+  </si>
+  <si>
     <t>31.170071</t>
   </si>
   <si>
@@ -1591,6 +1753,9 @@
     <t>POINT (121.508874 31.172159)</t>
   </si>
   <si>
+    <t>B0FFIXRYBW</t>
+  </si>
+  <si>
     <t>31.17091</t>
   </si>
   <si>
@@ -1609,6 +1774,9 @@
     <t>POINT (121.507692 31.172994)</t>
   </si>
   <si>
+    <t>B00156DD0X</t>
+  </si>
+  <si>
     <t>31.170147</t>
   </si>
   <si>
@@ -1627,6 +1795,9 @@
     <t>POINT (121.50816 31.172233)</t>
   </si>
   <si>
+    <t>B0G335WC6Q</t>
+  </si>
+  <si>
     <t>成山路800号云顶国际商业广场A座1106室</t>
   </si>
   <si>
@@ -1645,6 +1816,9 @@
     <t>POINT (121.509398 31.174026)</t>
   </si>
   <si>
+    <t>B0FFIXRFXV</t>
+  </si>
+  <si>
     <t>31.170382</t>
   </si>
   <si>
@@ -1663,6 +1837,9 @@
     <t>POINT (121.507456 31.172466)</t>
   </si>
   <si>
+    <t>B0FFIXRW4U</t>
+  </si>
+  <si>
     <t>31.171067</t>
   </si>
   <si>
@@ -1681,6 +1858,9 @@
     <t>POINT (121.508429 31.173153)</t>
   </si>
   <si>
+    <t>B0G0BO3X7E</t>
+  </si>
+  <si>
     <t>汽车服务</t>
   </si>
   <si>
@@ -1714,6 +1894,9 @@
     <t>POINT (121.509308 31.174679)</t>
   </si>
   <si>
+    <t>B0FFIXQ57O</t>
+  </si>
+  <si>
     <t>31.170646</t>
   </si>
   <si>
@@ -1732,6 +1915,9 @@
     <t>POINT (121.507876 31.172731)</t>
   </si>
   <si>
+    <t>B0FFIXQKIW</t>
+  </si>
+  <si>
     <t>31.169631</t>
   </si>
   <si>
@@ -1750,6 +1936,9 @@
     <t>POINT (121.508078 31.171717)</t>
   </si>
   <si>
+    <t>B0FFIXQTTI</t>
+  </si>
+  <si>
     <t>31.16985</t>
   </si>
   <si>
@@ -1768,6 +1957,9 @@
     <t>POINT (121.508017 31.171935)</t>
   </si>
   <si>
+    <t>B0FFHRISOV</t>
+  </si>
+  <si>
     <t>东明路1359附近</t>
   </si>
   <si>
@@ -1801,6 +1993,9 @@
     <t>POINT (121.506984 31.174377)</t>
   </si>
   <si>
+    <t>B0FFHEYN5K</t>
+  </si>
+  <si>
     <t>周家渡街道成山路800号云顶广场A座1101室</t>
   </si>
   <si>
@@ -1810,6 +2005,9 @@
     <t>021-68377063</t>
   </si>
   <si>
+    <t>B0GUU6Y64X</t>
+  </si>
+  <si>
     <t>成山路800号A座14楼</t>
   </si>
   <si>
@@ -1831,6 +2029,9 @@
     <t>POINT (121.509375 31.174637)</t>
   </si>
   <si>
+    <t>B0FFLBZVXI</t>
+  </si>
+  <si>
     <t>31.17162</t>
   </si>
   <si>
@@ -1849,6 +2050,9 @@
     <t>POINT (121.507712 31.173704)</t>
   </si>
   <si>
+    <t>B0FFIXRBEI</t>
+  </si>
+  <si>
     <t>31.170716</t>
   </si>
   <si>
@@ -1867,6 +2071,9 @@
     <t>POINT (121.508446 31.172802)</t>
   </si>
   <si>
+    <t>B001573322</t>
+  </si>
+  <si>
     <t>成山路800号云顶国际商业广场A座8层</t>
   </si>
   <si>
@@ -1891,6 +2098,9 @@
     <t>POINT (121.509483 31.174051)</t>
   </si>
   <si>
+    <t>B0FFIXPVP0</t>
+  </si>
+  <si>
     <t>31.17105</t>
   </si>
   <si>
@@ -1909,6 +2119,9 @@
     <t>POINT (121.508295 31.173136)</t>
   </si>
   <si>
+    <t>B0FFIXRJY4</t>
+  </si>
+  <si>
     <t>31.171022</t>
   </si>
   <si>
@@ -1927,9 +2140,15 @@
     <t>POINT (121.50808 31.173107)</t>
   </si>
   <si>
+    <t>B00156TH59</t>
+  </si>
+  <si>
     <t>周家渡街道恒大居委会综治工作站</t>
   </si>
   <si>
+    <t>B0G23XH18V</t>
+  </si>
+  <si>
     <t>31.170312</t>
   </si>
   <si>
@@ -1960,6 +2179,9 @@
     <t>POINT (121.507436 31.172395)</t>
   </si>
   <si>
+    <t>B0FFIXR8H9</t>
+  </si>
+  <si>
     <t>31.169576</t>
   </si>
   <si>
@@ -1978,6 +2200,9 @@
     <t>POINT (121.507744 31.171661)</t>
   </si>
   <si>
+    <t>B0FFIXQL3K</t>
+  </si>
+  <si>
     <t>31.169877</t>
   </si>
   <si>
@@ -1996,6 +2221,9 @@
     <t>POINT (121.508221 31.171963)</t>
   </si>
   <si>
+    <t>B0FFMB1XXE</t>
+  </si>
+  <si>
     <t>成山路800号云顶国际商业广场a座</t>
   </si>
   <si>
@@ -2020,6 +2248,9 @@
     <t>POINT (121.509407 31.174022)</t>
   </si>
   <si>
+    <t>B0HD7ORQXO</t>
+  </si>
+  <si>
     <t>成山路云顶广场</t>
   </si>
   <si>
@@ -2041,6 +2272,9 @@
     <t>POINT (121.509281 31.174803)</t>
   </si>
   <si>
+    <t>B0FFG780PZ</t>
+  </si>
+  <si>
     <t>成山路800号云顶广场A座</t>
   </si>
   <si>
@@ -2059,9 +2293,15 @@
     <t>POINT (121.509407 31.174029)</t>
   </si>
   <si>
+    <t>B0HA6RCDT9</t>
+  </si>
+  <si>
     <t>苏州威盛视信息科技有限公司</t>
   </si>
   <si>
+    <t>B0FFFOOBVA</t>
+  </si>
+  <si>
     <t>31.171178</t>
   </si>
   <si>
@@ -2080,6 +2320,9 @@
     <t>POINT (121.507189 31.17326)</t>
   </si>
   <si>
+    <t>B0FFIZIDEF</t>
+  </si>
+  <si>
     <t>成山路800号云顶国际A座1405</t>
   </si>
   <si>
@@ -2098,6 +2341,9 @@
     <t>071600</t>
   </si>
   <si>
+    <t>B0FFM81NWE</t>
+  </si>
+  <si>
     <t>周家渡街道成山路800号云顶大厦</t>
   </si>
   <si>
@@ -2119,6 +2365,9 @@
     <t>POINT (121.509459 31.174671)</t>
   </si>
   <si>
+    <t>B0FFFCCVV2</t>
+  </si>
+  <si>
     <t>成山路800号b2(邹平路)云顶广场</t>
   </si>
   <si>
@@ -2152,6 +2401,9 @@
     <t>POINT (121.509654 31.174868)</t>
   </si>
   <si>
+    <t>B0FFIXR0PG</t>
+  </si>
+  <si>
     <t>31.171321</t>
   </si>
   <si>
@@ -2170,12 +2422,21 @@
     <t>POINT (121.508251 31.173406)</t>
   </si>
   <si>
+    <t>B00156YOLM</t>
+  </si>
+  <si>
     <t>恒大居委党风廉政监督站</t>
   </si>
   <si>
+    <t>B00156YOLP</t>
+  </si>
+  <si>
     <t>中共恒大居民区总支委员会</t>
   </si>
   <si>
+    <t>B00155P61G</t>
+  </si>
+  <si>
     <t>31.170785</t>
   </si>
   <si>
@@ -2194,6 +2455,9 @@
     <t>POINT (121.507432 31.172868)</t>
   </si>
   <si>
+    <t>B0FFIXQUA2</t>
+  </si>
+  <si>
     <t>31.169709</t>
   </si>
   <si>
@@ -2212,6 +2476,9 @@
     <t>POINT (121.508637 31.171796)</t>
   </si>
   <si>
+    <t>B0FFIXRD3O</t>
+  </si>
+  <si>
     <t>31.170668</t>
   </si>
   <si>
@@ -2230,6 +2497,9 @@
     <t>POINT (121.508071 31.172753)</t>
   </si>
   <si>
+    <t>B0FFIXQBCQ</t>
+  </si>
+  <si>
     <t>31.17039</t>
   </si>
   <si>
@@ -2248,6 +2518,9 @@
     <t>POINT (121.508322 31.172476)</t>
   </si>
   <si>
+    <t>B0FFGQ6FG8</t>
+  </si>
+  <si>
     <t>31.169086</t>
   </si>
   <si>
@@ -2278,6 +2551,9 @@
     <t>POINT (121.507076 31.171169)</t>
   </si>
   <si>
+    <t>B0FFF8HOHX</t>
+  </si>
+  <si>
     <t>31.172392</t>
   </si>
   <si>
@@ -2296,6 +2572,9 @@
     <t>POINT (121.506968 31.174473)</t>
   </si>
   <si>
+    <t>B0FFIXQFGN</t>
+  </si>
+  <si>
     <t>31.170334</t>
   </si>
   <si>
@@ -2314,9 +2593,15 @@
     <t>POINT (121.507934 31.172419)</t>
   </si>
   <si>
+    <t>B0FFLLRK8V</t>
+  </si>
+  <si>
     <t>怪兽充电(宜必思酒店世博店)</t>
   </si>
   <si>
+    <t>B0FFIXS11K</t>
+  </si>
+  <si>
     <t>31.169681</t>
   </si>
   <si>
@@ -2335,6 +2620,9 @@
     <t>POINT (121.508448 31.171768)</t>
   </si>
   <si>
+    <t>B0FFLLLL3Q</t>
+  </si>
+  <si>
     <t>31.17273</t>
   </si>
   <si>
@@ -2353,6 +2641,9 @@
     <t>POINT (121.509495 31.174818)</t>
   </si>
   <si>
+    <t>B0FFIXQX8D</t>
+  </si>
+  <si>
     <t>31.170889</t>
   </si>
   <si>
@@ -2371,6 +2662,9 @@
     <t>POINT (121.5075 31.172972)</t>
   </si>
   <si>
+    <t>B0FFIXRJX9</t>
+  </si>
+  <si>
     <t>31.171342</t>
   </si>
   <si>
@@ -2389,6 +2683,9 @@
     <t>POINT (121.508368 31.173428)</t>
   </si>
   <si>
+    <t>B0HGP5SX7B</t>
+  </si>
+  <si>
     <t>成山路800号(东明路地铁站5号口步行220米)</t>
   </si>
   <si>
@@ -2410,6 +2707,9 @@
     <t>POINT (121.509931 31.17384)</t>
   </si>
   <si>
+    <t>B0FFG73GNH</t>
+  </si>
+  <si>
     <t>成山路800</t>
   </si>
   <si>
@@ -2429,6 +2729,9 @@
   </si>
   <si>
     <t>POINT (121.509353 31.174713)</t>
+  </si>
+  <si>
+    <t>B0H2C5TWBZ</t>
   </si>
   <si>
     <t>成山路800号云顶广场楼内</t>
@@ -2918,19 +3221,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
         <v>26</v>
@@ -2942,16 +3245,16 @@
         <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M3" t="s">
         <v>33</v>
@@ -2960,42 +3263,42 @@
         <v>28</v>
       </c>
       <c r="O3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P3" t="s">
         <v>35</v>
       </c>
       <c r="Q3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
         <v>26</v>
@@ -3007,16 +3310,16 @@
         <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M4" t="s">
         <v>33</v>
@@ -3025,36 +3328,36 @@
         <v>28</v>
       </c>
       <c r="O4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="S4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="U4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -3072,16 +3375,16 @@
         <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M5" t="s">
         <v>33</v>
@@ -3090,42 +3393,42 @@
         <v>28</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="P5" t="s">
         <v>35</v>
       </c>
       <c r="Q5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="R5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="S5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="T5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
@@ -3137,16 +3440,16 @@
         <v>28</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M6" t="s">
         <v>33</v>
@@ -3155,42 +3458,42 @@
         <v>28</v>
       </c>
       <c r="O6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="Q6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="R6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="S6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="T6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="U6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
@@ -3202,16 +3505,16 @@
         <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="M7" t="s">
         <v>33</v>
@@ -3220,45 +3523,45 @@
         <v>28</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P7" t="s">
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="R7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="S7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="T7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="U7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F8" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
@@ -3267,16 +3570,16 @@
         <v>28</v>
       </c>
       <c r="I8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J8" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K8" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s">
         <v>33</v>
@@ -3285,45 +3588,45 @@
         <v>28</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P8" t="s">
         <v>35</v>
       </c>
       <c r="Q8" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="R8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="T8" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="U8" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F9" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -3332,16 +3635,16 @@
         <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="J9" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="K9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="M9" t="s">
         <v>33</v>
@@ -3350,42 +3653,42 @@
         <v>28</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P9" t="s">
         <v>35</v>
       </c>
       <c r="Q9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="R9" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="S9" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="T9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="U9" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
@@ -3397,16 +3700,16 @@
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J10" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="K10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L10" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="M10" t="s">
         <v>33</v>
@@ -3415,42 +3718,42 @@
         <v>28</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P10" t="s">
         <v>35</v>
       </c>
       <c r="Q10" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="R10" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="S10" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="T10" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="U10" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
@@ -3462,16 +3765,16 @@
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="J11" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L11" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="M11" t="s">
         <v>33</v>
@@ -3480,42 +3783,42 @@
         <v>28</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P11" t="s">
         <v>35</v>
       </c>
       <c r="Q11" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="R11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="S11" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="T11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="U11" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
@@ -3527,16 +3830,16 @@
         <v>28</v>
       </c>
       <c r="I12" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="J12" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K12" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L12" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="M12" t="s">
         <v>33</v>
@@ -3545,45 +3848,45 @@
         <v>28</v>
       </c>
       <c r="O12" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="P12" t="s">
         <v>35</v>
       </c>
       <c r="Q12" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="R12" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="S12" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="T12" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="U12" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G13" t="s">
         <v>27</v>
@@ -3592,16 +3895,16 @@
         <v>28</v>
       </c>
       <c r="I13" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="J13" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="K13" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s">
         <v>33</v>
@@ -3610,42 +3913,42 @@
         <v>28</v>
       </c>
       <c r="O13" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="P13" t="s">
         <v>35</v>
       </c>
       <c r="Q13" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="R13" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="S13" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="T13" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="U13" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
@@ -3657,16 +3960,16 @@
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="J14" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K14" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="L14" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s">
         <v>33</v>
@@ -3675,42 +3978,42 @@
         <v>28</v>
       </c>
       <c r="O14" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="P14" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="Q14" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="R14" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="S14" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="T14" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="U14" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
@@ -3722,16 +4025,16 @@
         <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="K15" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s">
         <v>33</v>
@@ -3740,42 +4043,42 @@
         <v>28</v>
       </c>
       <c r="O15" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="Q15" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="R15" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="S15" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="T15" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="U15" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
@@ -3787,16 +4090,16 @@
         <v>28</v>
       </c>
       <c r="I16" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="J16" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="K16" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s">
         <v>33</v>
@@ -3805,42 +4108,42 @@
         <v>28</v>
       </c>
       <c r="O16" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="P16" t="s">
         <v>35</v>
       </c>
       <c r="Q16" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="R16" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="S16" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="T16" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="U16" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
@@ -3852,16 +4155,16 @@
         <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J17" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="K17" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="L17" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s">
         <v>33</v>
@@ -3870,42 +4173,42 @@
         <v>28</v>
       </c>
       <c r="O17" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="P17" t="s">
         <v>35</v>
       </c>
       <c r="Q17" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="R17" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="S17" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="T17" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -3917,16 +4220,16 @@
         <v>28</v>
       </c>
       <c r="I18" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J18" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="K18" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s">
         <v>33</v>
@@ -3935,42 +4238,42 @@
         <v>28</v>
       </c>
       <c r="O18" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="P18" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="Q18" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="R18" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="S18" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="T18" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="U18" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
@@ -3982,16 +4285,16 @@
         <v>28</v>
       </c>
       <c r="I19" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="J19" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="K19" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s">
         <v>33</v>
@@ -4000,42 +4303,42 @@
         <v>28</v>
       </c>
       <c r="O19" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="P19" t="s">
         <v>35</v>
       </c>
       <c r="Q19" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="R19" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="S19" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="T19" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="U19" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
@@ -4050,13 +4353,13 @@
         <v>29</v>
       </c>
       <c r="J20" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K20" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s">
         <v>33</v>
@@ -4065,30 +4368,30 @@
         <v>28</v>
       </c>
       <c r="O20" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="P20" t="s">
         <v>35</v>
       </c>
       <c r="Q20" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="R20" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="S20" t="s">
         <v>38</v>
       </c>
       <c r="T20" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="U20" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
@@ -4112,16 +4415,16 @@
         <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="J21" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="K21" t="s">
         <v>31</v>
       </c>
       <c r="L21" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s">
         <v>33</v>
@@ -4142,18 +4445,18 @@
         <v>37</v>
       </c>
       <c r="S21" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="T21" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="U21" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
@@ -4177,16 +4480,16 @@
         <v>28</v>
       </c>
       <c r="I22" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="J22" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K22" t="s">
         <v>31</v>
       </c>
       <c r="L22" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s">
         <v>33</v>
@@ -4207,18 +4510,18 @@
         <v>37</v>
       </c>
       <c r="S22" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="T22" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="U22" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -4242,16 +4545,16 @@
         <v>28</v>
       </c>
       <c r="I23" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="J23" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="K23" t="s">
         <v>31</v>
       </c>
       <c r="L23" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="M23" t="s">
         <v>33</v>
@@ -4263,7 +4566,7 @@
         <v>34</v>
       </c>
       <c r="P23" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="Q23" t="s">
         <v>36</v>
@@ -4272,30 +4575,30 @@
         <v>37</v>
       </c>
       <c r="S23" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="T23" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="U23" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
@@ -4307,16 +4610,16 @@
         <v>28</v>
       </c>
       <c r="I24" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="J24" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="K24" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="L24" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="M24" t="s">
         <v>33</v>
@@ -4325,42 +4628,42 @@
         <v>28</v>
       </c>
       <c r="O24" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="P24" t="s">
         <v>35</v>
       </c>
       <c r="Q24" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="R24" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="S24" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="T24" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="U24" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
@@ -4372,16 +4675,16 @@
         <v>28</v>
       </c>
       <c r="I25" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="J25" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="K25" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="L25" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s">
         <v>33</v>
@@ -4390,42 +4693,42 @@
         <v>28</v>
       </c>
       <c r="O25" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="P25" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="Q25" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="R25" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="S25" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="T25" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="U25" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
@@ -4437,16 +4740,16 @@
         <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="J26" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="K26" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="L26" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="M26" t="s">
         <v>33</v>
@@ -4455,42 +4758,42 @@
         <v>28</v>
       </c>
       <c r="O26" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s">
         <v>35</v>
       </c>
       <c r="Q26" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="R26" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="S26" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="T26" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="U26" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="B27" t="s">
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
@@ -4502,16 +4805,16 @@
         <v>28</v>
       </c>
       <c r="I27" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J27" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="K27" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="L27" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="M27" t="s">
         <v>33</v>
@@ -4520,42 +4823,42 @@
         <v>28</v>
       </c>
       <c r="O27" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="P27" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="Q27" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="R27" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="S27" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="T27" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="U27" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="B28" t="s">
         <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
@@ -4567,16 +4870,16 @@
         <v>28</v>
       </c>
       <c r="I28" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="J28" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="K28" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="L28" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="M28" t="s">
         <v>33</v>
@@ -4585,30 +4888,30 @@
         <v>28</v>
       </c>
       <c r="O28" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="P28" t="s">
         <v>35</v>
       </c>
       <c r="Q28" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="R28" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="S28" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="T28" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="U28" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
@@ -4620,7 +4923,7 @@
         <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
@@ -4632,16 +4935,16 @@
         <v>28</v>
       </c>
       <c r="I29" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="J29" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="K29" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L29" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s">
         <v>33</v>
@@ -4650,30 +4953,30 @@
         <v>28</v>
       </c>
       <c r="O29" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="P29" t="s">
         <v>35</v>
       </c>
       <c r="Q29" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="R29" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="S29" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="T29" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="U29" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
@@ -4685,7 +4988,7 @@
         <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
@@ -4697,16 +5000,16 @@
         <v>28</v>
       </c>
       <c r="I30" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="J30" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="K30" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="L30" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="M30" t="s">
         <v>33</v>
@@ -4715,42 +5018,42 @@
         <v>28</v>
       </c>
       <c r="O30" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="P30" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="Q30" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="R30" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="S30" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="T30" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="U30" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="B31" t="s">
         <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
@@ -4762,16 +5065,16 @@
         <v>28</v>
       </c>
       <c r="I31" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="J31" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="K31" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="L31" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="M31" t="s">
         <v>33</v>
@@ -4780,42 +5083,42 @@
         <v>28</v>
       </c>
       <c r="O31" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="P31" t="s">
         <v>35</v>
       </c>
       <c r="Q31" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="R31" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="S31" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="T31" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="U31" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s">
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
@@ -4827,16 +5130,16 @@
         <v>28</v>
       </c>
       <c r="I32" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="J32" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="K32" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="L32" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="M32" t="s">
         <v>33</v>
@@ -4845,42 +5148,42 @@
         <v>28</v>
       </c>
       <c r="O32" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="P32" t="s">
         <v>35</v>
       </c>
       <c r="Q32" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="R32" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="S32" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="T32" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="U32" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>348</v>
       </c>
       <c r="B33" t="s">
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="D33" t="s">
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
@@ -4892,16 +5195,16 @@
         <v>28</v>
       </c>
       <c r="I33" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="J33" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="K33" t="s">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="L33" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="M33" t="s">
         <v>33</v>
@@ -4910,42 +5213,42 @@
         <v>28</v>
       </c>
       <c r="O33" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="P33" t="s">
         <v>35</v>
       </c>
       <c r="Q33" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="R33" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="S33" t="s">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="T33" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="U33" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="D34" t="s">
         <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
@@ -4957,16 +5260,16 @@
         <v>28</v>
       </c>
       <c r="I34" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="J34" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="K34" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="L34" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="M34" t="s">
         <v>33</v>
@@ -4975,42 +5278,42 @@
         <v>28</v>
       </c>
       <c r="O34" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="P34" t="s">
         <v>35</v>
       </c>
       <c r="Q34" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="R34" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="S34" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="T34" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="U34" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="D35" t="s">
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
@@ -5022,16 +5325,16 @@
         <v>28</v>
       </c>
       <c r="I35" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="J35" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="K35" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L35" t="s">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="M35" t="s">
         <v>33</v>
@@ -5040,42 +5343,42 @@
         <v>28</v>
       </c>
       <c r="O35" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="P35" t="s">
         <v>35</v>
       </c>
       <c r="Q35" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="R35" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="S35" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="T35" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="U35" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
       </c>
       <c r="E36" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
@@ -5087,16 +5390,16 @@
         <v>28</v>
       </c>
       <c r="I36" t="s">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="J36" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="K36" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L36" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="M36" t="s">
         <v>33</v>
@@ -5105,42 +5408,42 @@
         <v>28</v>
       </c>
       <c r="O36" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="P36" t="s">
         <v>35</v>
       </c>
       <c r="Q36" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="R36" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="S36" t="s">
-        <v>358</v>
+        <v>392</v>
       </c>
       <c r="T36" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="U36" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="B37" t="s">
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>361</v>
+        <v>396</v>
       </c>
       <c r="D37" t="s">
         <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
@@ -5152,16 +5455,16 @@
         <v>28</v>
       </c>
       <c r="I37" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
       <c r="J37" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="K37" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L37" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="M37" t="s">
         <v>33</v>
@@ -5170,42 +5473,42 @@
         <v>28</v>
       </c>
       <c r="O37" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P37" t="s">
         <v>35</v>
       </c>
       <c r="Q37" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R37" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S37" t="s">
-        <v>368</v>
+        <v>403</v>
       </c>
       <c r="T37" t="s">
-        <v>369</v>
+        <v>404</v>
       </c>
       <c r="U37" t="s">
-        <v>370</v>
+        <v>405</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>406</v>
       </c>
       <c r="B38" t="s">
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
@@ -5217,16 +5520,16 @@
         <v>28</v>
       </c>
       <c r="I38" t="s">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="J38" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="K38" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="L38" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="M38" t="s">
         <v>33</v>
@@ -5235,42 +5538,42 @@
         <v>28</v>
       </c>
       <c r="O38" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="P38" t="s">
         <v>35</v>
       </c>
       <c r="Q38" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="R38" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="S38" t="s">
-        <v>368</v>
+        <v>403</v>
       </c>
       <c r="T38" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="U38" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>416</v>
       </c>
       <c r="B39" t="s">
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="D39" t="s">
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
@@ -5282,16 +5585,16 @@
         <v>28</v>
       </c>
       <c r="I39" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="J39" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="K39" t="s">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="L39" t="s">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="M39" t="s">
         <v>33</v>
@@ -5300,30 +5603,30 @@
         <v>28</v>
       </c>
       <c r="O39" t="s">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="P39" t="s">
         <v>35</v>
       </c>
       <c r="Q39" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="R39" t="s">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="S39" t="s">
-        <v>387</v>
+        <v>424</v>
       </c>
       <c r="T39" t="s">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="U39" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="B40" t="s">
         <v>22</v>
@@ -5335,7 +5638,7 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
@@ -5347,16 +5650,16 @@
         <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="J40" t="s">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="K40" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="L40" t="s">
-        <v>394</v>
+        <v>432</v>
       </c>
       <c r="M40" t="s">
         <v>33</v>
@@ -5365,42 +5668,42 @@
         <v>28</v>
       </c>
       <c r="O40" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="P40" t="s">
         <v>35</v>
       </c>
       <c r="Q40" t="s">
-        <v>395</v>
+        <v>433</v>
       </c>
       <c r="R40" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="S40" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="T40" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="U40" t="s">
-        <v>399</v>
+        <v>437</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="B41" t="s">
         <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>400</v>
+        <v>439</v>
       </c>
       <c r="D41" t="s">
         <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
@@ -5412,16 +5715,16 @@
         <v>28</v>
       </c>
       <c r="I41" t="s">
-        <v>401</v>
+        <v>440</v>
       </c>
       <c r="J41" t="s">
-        <v>402</v>
+        <v>441</v>
       </c>
       <c r="K41" t="s">
-        <v>403</v>
+        <v>442</v>
       </c>
       <c r="L41" t="s">
-        <v>404</v>
+        <v>443</v>
       </c>
       <c r="M41" t="s">
         <v>33</v>
@@ -5430,42 +5733,42 @@
         <v>28</v>
       </c>
       <c r="O41" t="s">
-        <v>403</v>
+        <v>442</v>
       </c>
       <c r="P41" t="s">
         <v>35</v>
       </c>
       <c r="Q41" t="s">
-        <v>405</v>
+        <v>444</v>
       </c>
       <c r="R41" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
       <c r="S41" t="s">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="T41" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="U41" t="s">
-        <v>409</v>
+        <v>448</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="B42" t="s">
         <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="D42" t="s">
         <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
@@ -5477,16 +5780,16 @@
         <v>28</v>
       </c>
       <c r="I42" t="s">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="J42" t="s">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="K42" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L42" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="M42" t="s">
         <v>33</v>
@@ -5495,30 +5798,30 @@
         <v>28</v>
       </c>
       <c r="O42" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P42" t="s">
         <v>35</v>
       </c>
       <c r="Q42" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R42" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S42" t="s">
-        <v>413</v>
+        <v>453</v>
       </c>
       <c r="T42" t="s">
-        <v>414</v>
+        <v>454</v>
       </c>
       <c r="U42" t="s">
-        <v>415</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c r="B43" t="s">
         <v>22</v>
@@ -5530,7 +5833,7 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
@@ -5542,16 +5845,16 @@
         <v>28</v>
       </c>
       <c r="I43" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="J43" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="K43" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="L43" t="s">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="M43" t="s">
         <v>33</v>
@@ -5560,42 +5863,42 @@
         <v>28</v>
       </c>
       <c r="O43" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="P43" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="Q43" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="R43" t="s">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="S43" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="T43" t="s">
-        <v>423</v>
+        <v>464</v>
       </c>
       <c r="U43" t="s">
-        <v>424</v>
+        <v>465</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="B44" t="s">
         <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>425</v>
+        <v>467</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
@@ -5607,16 +5910,16 @@
         <v>28</v>
       </c>
       <c r="I44" t="s">
-        <v>426</v>
+        <v>468</v>
       </c>
       <c r="J44" t="s">
-        <v>427</v>
+        <v>469</v>
       </c>
       <c r="K44" t="s">
-        <v>428</v>
+        <v>470</v>
       </c>
       <c r="L44" t="s">
-        <v>429</v>
+        <v>471</v>
       </c>
       <c r="M44" t="s">
         <v>33</v>
@@ -5625,42 +5928,42 @@
         <v>28</v>
       </c>
       <c r="O44" t="s">
-        <v>428</v>
+        <v>470</v>
       </c>
       <c r="P44" t="s">
-        <v>430</v>
+        <v>472</v>
       </c>
       <c r="Q44" t="s">
-        <v>431</v>
+        <v>473</v>
       </c>
       <c r="R44" t="s">
-        <v>432</v>
+        <v>474</v>
       </c>
       <c r="S44" t="s">
-        <v>433</v>
+        <v>475</v>
       </c>
       <c r="T44" t="s">
-        <v>434</v>
+        <v>476</v>
       </c>
       <c r="U44" t="s">
-        <v>435</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>478</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>436</v>
+        <v>479</v>
       </c>
       <c r="D45" t="s">
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>437</v>
+        <v>480</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
@@ -5672,16 +5975,16 @@
         <v>28</v>
       </c>
       <c r="I45" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="J45" t="s">
-        <v>439</v>
+        <v>482</v>
       </c>
       <c r="K45" t="s">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="L45" t="s">
-        <v>441</v>
+        <v>484</v>
       </c>
       <c r="M45" t="s">
         <v>33</v>
@@ -5690,42 +5993,42 @@
         <v>28</v>
       </c>
       <c r="O45" t="s">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="P45" t="s">
         <v>35</v>
       </c>
       <c r="Q45" t="s">
-        <v>442</v>
+        <v>485</v>
       </c>
       <c r="R45" t="s">
-        <v>443</v>
+        <v>486</v>
       </c>
       <c r="S45" t="s">
-        <v>444</v>
+        <v>487</v>
       </c>
       <c r="T45" t="s">
-        <v>445</v>
+        <v>488</v>
       </c>
       <c r="U45" t="s">
-        <v>446</v>
+        <v>489</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>490</v>
       </c>
       <c r="B46" t="s">
         <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>447</v>
+        <v>491</v>
       </c>
       <c r="D46" t="s">
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
@@ -5737,16 +6040,16 @@
         <v>28</v>
       </c>
       <c r="I46" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J46" t="s">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="K46" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L46" t="s">
-        <v>449</v>
+        <v>493</v>
       </c>
       <c r="M46" t="s">
         <v>33</v>
@@ -5755,42 +6058,42 @@
         <v>28</v>
       </c>
       <c r="O46" t="s">
-        <v>450</v>
+        <v>494</v>
       </c>
       <c r="P46" t="s">
-        <v>451</v>
+        <v>495</v>
       </c>
       <c r="Q46" t="s">
-        <v>452</v>
+        <v>496</v>
       </c>
       <c r="R46" t="s">
-        <v>453</v>
+        <v>497</v>
       </c>
       <c r="S46" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="T46" t="s">
-        <v>454</v>
+        <v>498</v>
       </c>
       <c r="U46" t="s">
-        <v>455</v>
+        <v>499</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="B47" t="s">
         <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D47" t="s">
         <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
@@ -5802,16 +6105,16 @@
         <v>28</v>
       </c>
       <c r="I47" t="s">
-        <v>457</v>
+        <v>502</v>
       </c>
       <c r="J47" t="s">
-        <v>458</v>
+        <v>503</v>
       </c>
       <c r="K47" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L47" t="s">
-        <v>460</v>
+        <v>505</v>
       </c>
       <c r="M47" t="s">
         <v>33</v>
@@ -5820,42 +6123,42 @@
         <v>28</v>
       </c>
       <c r="O47" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P47" t="s">
         <v>35</v>
       </c>
       <c r="Q47" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R47" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S47" t="s">
-        <v>464</v>
+        <v>509</v>
       </c>
       <c r="T47" t="s">
-        <v>465</v>
+        <v>510</v>
       </c>
       <c r="U47" t="s">
-        <v>466</v>
+        <v>511</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>512</v>
       </c>
       <c r="B48" t="s">
         <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D48" t="s">
         <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
@@ -5867,16 +6170,16 @@
         <v>28</v>
       </c>
       <c r="I48" t="s">
-        <v>467</v>
+        <v>513</v>
       </c>
       <c r="J48" t="s">
-        <v>468</v>
+        <v>514</v>
       </c>
       <c r="K48" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L48" t="s">
-        <v>469</v>
+        <v>515</v>
       </c>
       <c r="M48" t="s">
         <v>33</v>
@@ -5885,42 +6188,42 @@
         <v>28</v>
       </c>
       <c r="O48" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P48" t="s">
         <v>35</v>
       </c>
       <c r="Q48" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R48" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S48" t="s">
-        <v>470</v>
+        <v>516</v>
       </c>
       <c r="T48" t="s">
-        <v>471</v>
+        <v>517</v>
       </c>
       <c r="U48" t="s">
-        <v>472</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>519</v>
       </c>
       <c r="B49" t="s">
         <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
@@ -5932,16 +6235,16 @@
         <v>28</v>
       </c>
       <c r="I49" t="s">
-        <v>473</v>
+        <v>520</v>
       </c>
       <c r="J49" t="s">
-        <v>474</v>
+        <v>521</v>
       </c>
       <c r="K49" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L49" t="s">
-        <v>475</v>
+        <v>522</v>
       </c>
       <c r="M49" t="s">
         <v>33</v>
@@ -5950,42 +6253,42 @@
         <v>28</v>
       </c>
       <c r="O49" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P49" t="s">
         <v>35</v>
       </c>
       <c r="Q49" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R49" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S49" t="s">
-        <v>476</v>
+        <v>523</v>
       </c>
       <c r="T49" t="s">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="U49" t="s">
-        <v>478</v>
+        <v>525</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>526</v>
       </c>
       <c r="B50" t="s">
         <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D50" t="s">
         <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
@@ -5997,16 +6300,16 @@
         <v>28</v>
       </c>
       <c r="I50" t="s">
-        <v>479</v>
+        <v>527</v>
       </c>
       <c r="J50" t="s">
-        <v>480</v>
+        <v>528</v>
       </c>
       <c r="K50" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L50" t="s">
-        <v>481</v>
+        <v>529</v>
       </c>
       <c r="M50" t="s">
         <v>33</v>
@@ -6015,42 +6318,42 @@
         <v>28</v>
       </c>
       <c r="O50" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P50" t="s">
         <v>35</v>
       </c>
       <c r="Q50" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R50" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S50" t="s">
-        <v>482</v>
+        <v>530</v>
       </c>
       <c r="T50" t="s">
-        <v>483</v>
+        <v>531</v>
       </c>
       <c r="U50" t="s">
-        <v>484</v>
+        <v>532</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>533</v>
       </c>
       <c r="B51" t="s">
         <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>485</v>
+        <v>534</v>
       </c>
       <c r="D51" t="s">
         <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
@@ -6062,16 +6365,16 @@
         <v>28</v>
       </c>
       <c r="I51" t="s">
-        <v>486</v>
+        <v>535</v>
       </c>
       <c r="J51" t="s">
-        <v>487</v>
+        <v>536</v>
       </c>
       <c r="K51" t="s">
-        <v>488</v>
+        <v>537</v>
       </c>
       <c r="L51" t="s">
-        <v>489</v>
+        <v>538</v>
       </c>
       <c r="M51" t="s">
         <v>33</v>
@@ -6080,42 +6383,42 @@
         <v>28</v>
       </c>
       <c r="O51" t="s">
-        <v>488</v>
+        <v>537</v>
       </c>
       <c r="P51" t="s">
         <v>35</v>
       </c>
       <c r="Q51" t="s">
-        <v>490</v>
+        <v>539</v>
       </c>
       <c r="R51" t="s">
-        <v>491</v>
+        <v>540</v>
       </c>
       <c r="S51" t="s">
-        <v>492</v>
+        <v>541</v>
       </c>
       <c r="T51" t="s">
-        <v>493</v>
+        <v>542</v>
       </c>
       <c r="U51" t="s">
-        <v>494</v>
+        <v>543</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>544</v>
       </c>
       <c r="B52" t="s">
         <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
@@ -6127,16 +6430,16 @@
         <v>28</v>
       </c>
       <c r="I52" t="s">
-        <v>495</v>
+        <v>545</v>
       </c>
       <c r="J52" t="s">
-        <v>496</v>
+        <v>546</v>
       </c>
       <c r="K52" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L52" t="s">
-        <v>497</v>
+        <v>547</v>
       </c>
       <c r="M52" t="s">
         <v>33</v>
@@ -6145,42 +6448,42 @@
         <v>28</v>
       </c>
       <c r="O52" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P52" t="s">
         <v>35</v>
       </c>
       <c r="Q52" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R52" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S52" t="s">
-        <v>498</v>
+        <v>548</v>
       </c>
       <c r="T52" t="s">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="U52" t="s">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>21</v>
+        <v>551</v>
       </c>
       <c r="B53" t="s">
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D53" t="s">
         <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
@@ -6192,16 +6495,16 @@
         <v>28</v>
       </c>
       <c r="I53" t="s">
-        <v>501</v>
+        <v>552</v>
       </c>
       <c r="J53" t="s">
-        <v>502</v>
+        <v>553</v>
       </c>
       <c r="K53" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L53" t="s">
-        <v>503</v>
+        <v>554</v>
       </c>
       <c r="M53" t="s">
         <v>33</v>
@@ -6210,42 +6513,42 @@
         <v>28</v>
       </c>
       <c r="O53" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P53" t="s">
         <v>35</v>
       </c>
       <c r="Q53" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R53" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S53" t="s">
-        <v>504</v>
+        <v>555</v>
       </c>
       <c r="T53" t="s">
-        <v>505</v>
+        <v>556</v>
       </c>
       <c r="U53" t="s">
-        <v>506</v>
+        <v>557</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>558</v>
       </c>
       <c r="B54" t="s">
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
@@ -6257,16 +6560,16 @@
         <v>28</v>
       </c>
       <c r="I54" t="s">
-        <v>507</v>
+        <v>559</v>
       </c>
       <c r="J54" t="s">
-        <v>508</v>
+        <v>560</v>
       </c>
       <c r="K54" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L54" t="s">
-        <v>509</v>
+        <v>561</v>
       </c>
       <c r="M54" t="s">
         <v>33</v>
@@ -6275,42 +6578,42 @@
         <v>28</v>
       </c>
       <c r="O54" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P54" t="s">
         <v>35</v>
       </c>
       <c r="Q54" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R54" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S54" t="s">
-        <v>510</v>
+        <v>562</v>
       </c>
       <c r="T54" t="s">
-        <v>511</v>
+        <v>563</v>
       </c>
       <c r="U54" t="s">
-        <v>512</v>
+        <v>564</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>565</v>
       </c>
       <c r="B55" t="s">
         <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D55" t="s">
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
@@ -6322,16 +6625,16 @@
         <v>28</v>
       </c>
       <c r="I55" t="s">
-        <v>513</v>
+        <v>566</v>
       </c>
       <c r="J55" t="s">
-        <v>514</v>
+        <v>567</v>
       </c>
       <c r="K55" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L55" t="s">
-        <v>515</v>
+        <v>568</v>
       </c>
       <c r="M55" t="s">
         <v>33</v>
@@ -6340,42 +6643,42 @@
         <v>28</v>
       </c>
       <c r="O55" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P55" t="s">
         <v>35</v>
       </c>
       <c r="Q55" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R55" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S55" t="s">
-        <v>516</v>
+        <v>569</v>
       </c>
       <c r="T55" t="s">
-        <v>517</v>
+        <v>570</v>
       </c>
       <c r="U55" t="s">
-        <v>518</v>
+        <v>571</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>572</v>
       </c>
       <c r="B56" t="s">
         <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D56" t="s">
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
@@ -6387,16 +6690,16 @@
         <v>28</v>
       </c>
       <c r="I56" t="s">
-        <v>519</v>
+        <v>573</v>
       </c>
       <c r="J56" t="s">
-        <v>520</v>
+        <v>574</v>
       </c>
       <c r="K56" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L56" t="s">
-        <v>521</v>
+        <v>575</v>
       </c>
       <c r="M56" t="s">
         <v>33</v>
@@ -6405,42 +6708,42 @@
         <v>28</v>
       </c>
       <c r="O56" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P56" t="s">
         <v>35</v>
       </c>
       <c r="Q56" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R56" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S56" t="s">
-        <v>522</v>
+        <v>576</v>
       </c>
       <c r="T56" t="s">
-        <v>523</v>
+        <v>577</v>
       </c>
       <c r="U56" t="s">
-        <v>524</v>
+        <v>578</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>21</v>
+        <v>579</v>
       </c>
       <c r="B57" t="s">
         <v>22</v>
       </c>
       <c r="C57" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
@@ -6452,16 +6755,16 @@
         <v>28</v>
       </c>
       <c r="I57" t="s">
-        <v>525</v>
+        <v>580</v>
       </c>
       <c r="J57" t="s">
-        <v>526</v>
+        <v>581</v>
       </c>
       <c r="K57" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L57" t="s">
-        <v>527</v>
+        <v>582</v>
       </c>
       <c r="M57" t="s">
         <v>33</v>
@@ -6470,36 +6773,36 @@
         <v>28</v>
       </c>
       <c r="O57" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P57" t="s">
         <v>35</v>
       </c>
       <c r="Q57" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R57" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S57" t="s">
-        <v>528</v>
+        <v>583</v>
       </c>
       <c r="T57" t="s">
-        <v>529</v>
+        <v>584</v>
       </c>
       <c r="U57" t="s">
-        <v>530</v>
+        <v>585</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>586</v>
       </c>
       <c r="B58" t="s">
         <v>22</v>
       </c>
       <c r="C58" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D58" t="s">
         <v>24</v>
@@ -6517,16 +6820,16 @@
         <v>28</v>
       </c>
       <c r="I58" t="s">
-        <v>531</v>
+        <v>587</v>
       </c>
       <c r="J58" t="s">
-        <v>532</v>
+        <v>588</v>
       </c>
       <c r="K58" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L58" t="s">
-        <v>533</v>
+        <v>589</v>
       </c>
       <c r="M58" t="s">
         <v>33</v>
@@ -6535,42 +6838,42 @@
         <v>28</v>
       </c>
       <c r="O58" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="P58" t="s">
         <v>35</v>
       </c>
       <c r="Q58" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="R58" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="S58" t="s">
-        <v>534</v>
+        <v>590</v>
       </c>
       <c r="T58" t="s">
-        <v>535</v>
+        <v>591</v>
       </c>
       <c r="U58" t="s">
-        <v>536</v>
+        <v>592</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>593</v>
       </c>
       <c r="B59" t="s">
         <v>22</v>
       </c>
       <c r="C59" t="s">
-        <v>537</v>
+        <v>594</v>
       </c>
       <c r="D59" t="s">
         <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
@@ -6582,16 +6885,16 @@
         <v>28</v>
       </c>
       <c r="I59" t="s">
-        <v>538</v>
+        <v>595</v>
       </c>
       <c r="J59" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="K59" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L59" t="s">
-        <v>539</v>
+        <v>596</v>
       </c>
       <c r="M59" t="s">
         <v>33</v>
@@ -6600,42 +6903,42 @@
         <v>28</v>
       </c>
       <c r="O59" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P59" t="s">
-        <v>540</v>
+        <v>597</v>
       </c>
       <c r="Q59" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R59" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S59" t="s">
-        <v>541</v>
+        <v>598</v>
       </c>
       <c r="T59" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="U59" t="s">
-        <v>542</v>
+        <v>599</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>600</v>
       </c>
       <c r="B60" t="s">
         <v>22</v>
       </c>
       <c r="C60" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
@@ -6647,16 +6950,16 @@
         <v>28</v>
       </c>
       <c r="I60" t="s">
-        <v>543</v>
+        <v>601</v>
       </c>
       <c r="J60" t="s">
-        <v>544</v>
+        <v>602</v>
       </c>
       <c r="K60" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L60" t="s">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="M60" t="s">
         <v>33</v>
@@ -6665,42 +6968,42 @@
         <v>28</v>
       </c>
       <c r="O60" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P60" t="s">
         <v>35</v>
       </c>
       <c r="Q60" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R60" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S60" t="s">
-        <v>546</v>
+        <v>604</v>
       </c>
       <c r="T60" t="s">
-        <v>547</v>
+        <v>605</v>
       </c>
       <c r="U60" t="s">
-        <v>548</v>
+        <v>606</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>607</v>
       </c>
       <c r="B61" t="s">
         <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
@@ -6712,16 +7015,16 @@
         <v>28</v>
       </c>
       <c r="I61" t="s">
-        <v>549</v>
+        <v>608</v>
       </c>
       <c r="J61" t="s">
-        <v>550</v>
+        <v>609</v>
       </c>
       <c r="K61" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L61" t="s">
-        <v>551</v>
+        <v>610</v>
       </c>
       <c r="M61" t="s">
         <v>33</v>
@@ -6730,30 +7033,30 @@
         <v>28</v>
       </c>
       <c r="O61" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P61" t="s">
         <v>35</v>
       </c>
       <c r="Q61" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R61" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S61" t="s">
-        <v>552</v>
+        <v>611</v>
       </c>
       <c r="T61" t="s">
-        <v>553</v>
+        <v>612</v>
       </c>
       <c r="U61" t="s">
-        <v>554</v>
+        <v>613</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>614</v>
       </c>
       <c r="B62" t="s">
         <v>22</v>
@@ -6765,7 +7068,7 @@
         <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>555</v>
+        <v>615</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
@@ -6777,16 +7080,16 @@
         <v>28</v>
       </c>
       <c r="I62" t="s">
-        <v>556</v>
+        <v>616</v>
       </c>
       <c r="J62" t="s">
-        <v>557</v>
+        <v>617</v>
       </c>
       <c r="K62" t="s">
-        <v>558</v>
+        <v>618</v>
       </c>
       <c r="L62" t="s">
-        <v>559</v>
+        <v>619</v>
       </c>
       <c r="M62" t="s">
         <v>33</v>
@@ -6795,42 +7098,42 @@
         <v>28</v>
       </c>
       <c r="O62" t="s">
-        <v>558</v>
+        <v>618</v>
       </c>
       <c r="P62" t="s">
-        <v>560</v>
+        <v>620</v>
       </c>
       <c r="Q62" t="s">
-        <v>561</v>
+        <v>621</v>
       </c>
       <c r="R62" t="s">
-        <v>562</v>
+        <v>622</v>
       </c>
       <c r="S62" t="s">
-        <v>563</v>
+        <v>623</v>
       </c>
       <c r="T62" t="s">
-        <v>564</v>
+        <v>624</v>
       </c>
       <c r="U62" t="s">
-        <v>565</v>
+        <v>625</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>626</v>
       </c>
       <c r="B63" t="s">
         <v>22</v>
       </c>
       <c r="C63" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
@@ -6842,16 +7145,16 @@
         <v>28</v>
       </c>
       <c r="I63" t="s">
-        <v>566</v>
+        <v>627</v>
       </c>
       <c r="J63" t="s">
-        <v>567</v>
+        <v>628</v>
       </c>
       <c r="K63" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L63" t="s">
-        <v>568</v>
+        <v>629</v>
       </c>
       <c r="M63" t="s">
         <v>33</v>
@@ -6860,42 +7163,42 @@
         <v>28</v>
       </c>
       <c r="O63" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P63" t="s">
         <v>35</v>
       </c>
       <c r="Q63" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R63" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S63" t="s">
-        <v>569</v>
+        <v>630</v>
       </c>
       <c r="T63" t="s">
-        <v>570</v>
+        <v>631</v>
       </c>
       <c r="U63" t="s">
-        <v>571</v>
+        <v>632</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>633</v>
       </c>
       <c r="B64" t="s">
         <v>22</v>
       </c>
       <c r="C64" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
@@ -6907,16 +7210,16 @@
         <v>28</v>
       </c>
       <c r="I64" t="s">
-        <v>572</v>
+        <v>634</v>
       </c>
       <c r="J64" t="s">
-        <v>573</v>
+        <v>635</v>
       </c>
       <c r="K64" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L64" t="s">
-        <v>574</v>
+        <v>636</v>
       </c>
       <c r="M64" t="s">
         <v>33</v>
@@ -6925,42 +7228,42 @@
         <v>28</v>
       </c>
       <c r="O64" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P64" t="s">
         <v>35</v>
       </c>
       <c r="Q64" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R64" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S64" t="s">
-        <v>575</v>
+        <v>637</v>
       </c>
       <c r="T64" t="s">
-        <v>576</v>
+        <v>638</v>
       </c>
       <c r="U64" t="s">
-        <v>577</v>
+        <v>639</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>21</v>
+        <v>640</v>
       </c>
       <c r="B65" t="s">
         <v>22</v>
       </c>
       <c r="C65" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
@@ -6972,16 +7275,16 @@
         <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>578</v>
+        <v>641</v>
       </c>
       <c r="J65" t="s">
-        <v>579</v>
+        <v>642</v>
       </c>
       <c r="K65" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L65" t="s">
-        <v>580</v>
+        <v>643</v>
       </c>
       <c r="M65" t="s">
         <v>33</v>
@@ -6990,42 +7293,42 @@
         <v>28</v>
       </c>
       <c r="O65" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P65" t="s">
         <v>35</v>
       </c>
       <c r="Q65" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R65" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S65" t="s">
-        <v>581</v>
+        <v>644</v>
       </c>
       <c r="T65" t="s">
-        <v>582</v>
+        <v>645</v>
       </c>
       <c r="U65" t="s">
-        <v>583</v>
+        <v>646</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>647</v>
       </c>
       <c r="B66" t="s">
         <v>22</v>
       </c>
       <c r="C66" t="s">
-        <v>584</v>
+        <v>648</v>
       </c>
       <c r="D66" t="s">
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
@@ -7037,16 +7340,16 @@
         <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>585</v>
+        <v>649</v>
       </c>
       <c r="J66" t="s">
-        <v>586</v>
+        <v>650</v>
       </c>
       <c r="K66" t="s">
-        <v>587</v>
+        <v>651</v>
       </c>
       <c r="L66" t="s">
-        <v>588</v>
+        <v>652</v>
       </c>
       <c r="M66" t="s">
         <v>33</v>
@@ -7055,42 +7358,42 @@
         <v>28</v>
       </c>
       <c r="O66" t="s">
-        <v>589</v>
+        <v>653</v>
       </c>
       <c r="P66" t="s">
         <v>35</v>
       </c>
       <c r="Q66" t="s">
-        <v>590</v>
+        <v>654</v>
       </c>
       <c r="R66" t="s">
-        <v>591</v>
+        <v>655</v>
       </c>
       <c r="S66" t="s">
-        <v>592</v>
+        <v>656</v>
       </c>
       <c r="T66" t="s">
-        <v>593</v>
+        <v>657</v>
       </c>
       <c r="U66" t="s">
-        <v>594</v>
+        <v>658</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>659</v>
       </c>
       <c r="B67" t="s">
         <v>22</v>
       </c>
       <c r="C67" t="s">
-        <v>595</v>
+        <v>660</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
@@ -7102,16 +7405,16 @@
         <v>28</v>
       </c>
       <c r="I67" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="J67" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="K67" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L67" t="s">
-        <v>596</v>
+        <v>661</v>
       </c>
       <c r="M67" t="s">
         <v>33</v>
@@ -7120,42 +7423,42 @@
         <v>28</v>
       </c>
       <c r="O67" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P67" t="s">
-        <v>597</v>
+        <v>662</v>
       </c>
       <c r="Q67" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R67" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S67" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="T67" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="U67" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>663</v>
       </c>
       <c r="B68" t="s">
         <v>22</v>
       </c>
       <c r="C68" t="s">
-        <v>598</v>
+        <v>664</v>
       </c>
       <c r="D68" t="s">
         <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
@@ -7167,16 +7470,16 @@
         <v>28</v>
       </c>
       <c r="I68" t="s">
-        <v>599</v>
+        <v>665</v>
       </c>
       <c r="J68" t="s">
-        <v>600</v>
+        <v>666</v>
       </c>
       <c r="K68" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="L68" t="s">
-        <v>601</v>
+        <v>667</v>
       </c>
       <c r="M68" t="s">
         <v>33</v>
@@ -7185,42 +7488,42 @@
         <v>28</v>
       </c>
       <c r="O68" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="P68" t="s">
         <v>35</v>
       </c>
       <c r="Q68" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="R68" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="S68" t="s">
-        <v>602</v>
+        <v>668</v>
       </c>
       <c r="T68" t="s">
-        <v>603</v>
+        <v>669</v>
       </c>
       <c r="U68" t="s">
-        <v>604</v>
+        <v>670</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>671</v>
       </c>
       <c r="B69" t="s">
         <v>22</v>
       </c>
       <c r="C69" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D69" t="s">
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
@@ -7232,16 +7535,16 @@
         <v>28</v>
       </c>
       <c r="I69" t="s">
-        <v>605</v>
+        <v>672</v>
       </c>
       <c r="J69" t="s">
-        <v>606</v>
+        <v>673</v>
       </c>
       <c r="K69" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L69" t="s">
-        <v>607</v>
+        <v>674</v>
       </c>
       <c r="M69" t="s">
         <v>33</v>
@@ -7250,42 +7553,42 @@
         <v>28</v>
       </c>
       <c r="O69" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P69" t="s">
         <v>35</v>
       </c>
       <c r="Q69" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R69" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S69" t="s">
-        <v>608</v>
+        <v>675</v>
       </c>
       <c r="T69" t="s">
-        <v>609</v>
+        <v>676</v>
       </c>
       <c r="U69" t="s">
-        <v>610</v>
+        <v>677</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>678</v>
       </c>
       <c r="B70" t="s">
         <v>22</v>
       </c>
       <c r="C70" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
@@ -7297,16 +7600,16 @@
         <v>28</v>
       </c>
       <c r="I70" t="s">
-        <v>611</v>
+        <v>679</v>
       </c>
       <c r="J70" t="s">
-        <v>612</v>
+        <v>680</v>
       </c>
       <c r="K70" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L70" t="s">
-        <v>613</v>
+        <v>681</v>
       </c>
       <c r="M70" t="s">
         <v>33</v>
@@ -7315,42 +7618,42 @@
         <v>28</v>
       </c>
       <c r="O70" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P70" t="s">
         <v>35</v>
       </c>
       <c r="Q70" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R70" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S70" t="s">
-        <v>614</v>
+        <v>682</v>
       </c>
       <c r="T70" t="s">
-        <v>615</v>
+        <v>683</v>
       </c>
       <c r="U70" t="s">
-        <v>616</v>
+        <v>684</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>21</v>
+        <v>685</v>
       </c>
       <c r="B71" t="s">
         <v>22</v>
       </c>
       <c r="C71" t="s">
-        <v>617</v>
+        <v>686</v>
       </c>
       <c r="D71" t="s">
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
@@ -7362,16 +7665,16 @@
         <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>618</v>
+        <v>687</v>
       </c>
       <c r="J71" t="s">
-        <v>619</v>
+        <v>688</v>
       </c>
       <c r="K71" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L71" t="s">
-        <v>620</v>
+        <v>689</v>
       </c>
       <c r="M71" t="s">
         <v>33</v>
@@ -7380,42 +7683,42 @@
         <v>28</v>
       </c>
       <c r="O71" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P71" t="s">
-        <v>621</v>
+        <v>690</v>
       </c>
       <c r="Q71" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R71" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S71" t="s">
-        <v>622</v>
+        <v>691</v>
       </c>
       <c r="T71" t="s">
-        <v>623</v>
+        <v>692</v>
       </c>
       <c r="U71" t="s">
-        <v>624</v>
+        <v>693</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>694</v>
       </c>
       <c r="B72" t="s">
         <v>22</v>
       </c>
       <c r="C72" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
@@ -7427,16 +7730,16 @@
         <v>28</v>
       </c>
       <c r="I72" t="s">
-        <v>625</v>
+        <v>695</v>
       </c>
       <c r="J72" t="s">
-        <v>626</v>
+        <v>696</v>
       </c>
       <c r="K72" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L72" t="s">
-        <v>627</v>
+        <v>697</v>
       </c>
       <c r="M72" t="s">
         <v>33</v>
@@ -7445,42 +7748,42 @@
         <v>28</v>
       </c>
       <c r="O72" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P72" t="s">
         <v>35</v>
       </c>
       <c r="Q72" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R72" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S72" t="s">
-        <v>628</v>
+        <v>698</v>
       </c>
       <c r="T72" t="s">
-        <v>629</v>
+        <v>699</v>
       </c>
       <c r="U72" t="s">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>21</v>
+        <v>701</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
@@ -7492,16 +7795,16 @@
         <v>28</v>
       </c>
       <c r="I73" t="s">
-        <v>631</v>
+        <v>702</v>
       </c>
       <c r="J73" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="K73" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L73" t="s">
-        <v>633</v>
+        <v>704</v>
       </c>
       <c r="M73" t="s">
         <v>33</v>
@@ -7510,42 +7813,42 @@
         <v>28</v>
       </c>
       <c r="O73" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P73" t="s">
         <v>35</v>
       </c>
       <c r="Q73" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R73" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S73" t="s">
-        <v>634</v>
+        <v>705</v>
       </c>
       <c r="T73" t="s">
-        <v>635</v>
+        <v>706</v>
       </c>
       <c r="U73" t="s">
-        <v>636</v>
+        <v>707</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>21</v>
+        <v>708</v>
       </c>
       <c r="B74" t="s">
         <v>22</v>
       </c>
       <c r="C74" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D74" t="s">
         <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
@@ -7557,16 +7860,16 @@
         <v>28</v>
       </c>
       <c r="I74" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J74" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="K74" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="L74" t="s">
-        <v>637</v>
+        <v>709</v>
       </c>
       <c r="M74" t="s">
         <v>33</v>
@@ -7575,30 +7878,30 @@
         <v>28</v>
       </c>
       <c r="O74" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="P74" t="s">
         <v>35</v>
       </c>
       <c r="Q74" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="R74" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="S74" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="T74" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="U74" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>21</v>
+        <v>710</v>
       </c>
       <c r="B75" t="s">
         <v>22</v>
@@ -7610,7 +7913,7 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
@@ -7622,16 +7925,16 @@
         <v>28</v>
       </c>
       <c r="I75" t="s">
-        <v>638</v>
+        <v>711</v>
       </c>
       <c r="J75" t="s">
-        <v>639</v>
+        <v>712</v>
       </c>
       <c r="K75" t="s">
-        <v>640</v>
+        <v>713</v>
       </c>
       <c r="L75" t="s">
-        <v>641</v>
+        <v>714</v>
       </c>
       <c r="M75" t="s">
         <v>33</v>
@@ -7640,42 +7943,42 @@
         <v>28</v>
       </c>
       <c r="O75" t="s">
-        <v>642</v>
+        <v>715</v>
       </c>
       <c r="P75" t="s">
         <v>35</v>
       </c>
       <c r="Q75" t="s">
-        <v>643</v>
+        <v>716</v>
       </c>
       <c r="R75" t="s">
-        <v>644</v>
+        <v>717</v>
       </c>
       <c r="S75" t="s">
-        <v>645</v>
+        <v>718</v>
       </c>
       <c r="T75" t="s">
-        <v>646</v>
+        <v>719</v>
       </c>
       <c r="U75" t="s">
-        <v>647</v>
+        <v>720</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>21</v>
+        <v>721</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
@@ -7687,16 +7990,16 @@
         <v>28</v>
       </c>
       <c r="I76" t="s">
-        <v>648</v>
+        <v>722</v>
       </c>
       <c r="J76" t="s">
-        <v>649</v>
+        <v>723</v>
       </c>
       <c r="K76" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L76" t="s">
-        <v>650</v>
+        <v>724</v>
       </c>
       <c r="M76" t="s">
         <v>33</v>
@@ -7705,42 +8008,42 @@
         <v>28</v>
       </c>
       <c r="O76" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P76" t="s">
         <v>35</v>
       </c>
       <c r="Q76" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R76" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S76" t="s">
-        <v>651</v>
+        <v>725</v>
       </c>
       <c r="T76" t="s">
-        <v>652</v>
+        <v>726</v>
       </c>
       <c r="U76" t="s">
-        <v>653</v>
+        <v>727</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>728</v>
       </c>
       <c r="B77" t="s">
         <v>22</v>
       </c>
       <c r="C77" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D77" t="s">
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
@@ -7752,16 +8055,16 @@
         <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>654</v>
+        <v>729</v>
       </c>
       <c r="J77" t="s">
-        <v>655</v>
+        <v>730</v>
       </c>
       <c r="K77" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L77" t="s">
-        <v>656</v>
+        <v>731</v>
       </c>
       <c r="M77" t="s">
         <v>33</v>
@@ -7770,42 +8073,42 @@
         <v>28</v>
       </c>
       <c r="O77" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P77" t="s">
         <v>35</v>
       </c>
       <c r="Q77" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R77" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S77" t="s">
-        <v>657</v>
+        <v>732</v>
       </c>
       <c r="T77" t="s">
-        <v>658</v>
+        <v>733</v>
       </c>
       <c r="U77" t="s">
-        <v>659</v>
+        <v>734</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>21</v>
+        <v>735</v>
       </c>
       <c r="B78" t="s">
         <v>22</v>
       </c>
       <c r="C78" t="s">
-        <v>660</v>
+        <v>736</v>
       </c>
       <c r="D78" t="s">
         <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
@@ -7817,16 +8120,16 @@
         <v>28</v>
       </c>
       <c r="I78" t="s">
-        <v>661</v>
+        <v>737</v>
       </c>
       <c r="J78" t="s">
-        <v>662</v>
+        <v>738</v>
       </c>
       <c r="K78" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L78" t="s">
-        <v>663</v>
+        <v>739</v>
       </c>
       <c r="M78" t="s">
         <v>33</v>
@@ -7835,42 +8138,42 @@
         <v>28</v>
       </c>
       <c r="O78" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P78" t="s">
-        <v>664</v>
+        <v>740</v>
       </c>
       <c r="Q78" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R78" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S78" t="s">
-        <v>665</v>
+        <v>741</v>
       </c>
       <c r="T78" t="s">
-        <v>666</v>
+        <v>742</v>
       </c>
       <c r="U78" t="s">
-        <v>667</v>
+        <v>743</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>21</v>
+        <v>744</v>
       </c>
       <c r="B79" t="s">
         <v>22</v>
       </c>
       <c r="C79" t="s">
-        <v>668</v>
+        <v>745</v>
       </c>
       <c r="D79" t="s">
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
@@ -7882,16 +8185,16 @@
         <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>669</v>
+        <v>746</v>
       </c>
       <c r="J79" t="s">
-        <v>670</v>
+        <v>747</v>
       </c>
       <c r="K79" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L79" t="s">
-        <v>671</v>
+        <v>748</v>
       </c>
       <c r="M79" t="s">
         <v>33</v>
@@ -7900,42 +8203,42 @@
         <v>28</v>
       </c>
       <c r="O79" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P79" t="s">
         <v>35</v>
       </c>
       <c r="Q79" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R79" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S79" t="s">
-        <v>672</v>
+        <v>749</v>
       </c>
       <c r="T79" t="s">
-        <v>673</v>
+        <v>750</v>
       </c>
       <c r="U79" t="s">
-        <v>674</v>
+        <v>751</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>752</v>
       </c>
       <c r="B80" t="s">
         <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>675</v>
+        <v>753</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
@@ -7947,16 +8250,16 @@
         <v>28</v>
       </c>
       <c r="I80" t="s">
-        <v>676</v>
+        <v>754</v>
       </c>
       <c r="J80" t="s">
-        <v>662</v>
+        <v>738</v>
       </c>
       <c r="K80" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L80" t="s">
-        <v>677</v>
+        <v>755</v>
       </c>
       <c r="M80" t="s">
         <v>33</v>
@@ -7965,42 +8268,42 @@
         <v>28</v>
       </c>
       <c r="O80" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P80" t="s">
-        <v>678</v>
+        <v>756</v>
       </c>
       <c r="Q80" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R80" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S80" t="s">
-        <v>679</v>
+        <v>757</v>
       </c>
       <c r="T80" t="s">
-        <v>666</v>
+        <v>742</v>
       </c>
       <c r="U80" t="s">
-        <v>680</v>
+        <v>758</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>759</v>
       </c>
       <c r="B81" t="s">
         <v>22</v>
       </c>
       <c r="C81" t="s">
-        <v>660</v>
+        <v>736</v>
       </c>
       <c r="D81" t="s">
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
@@ -8012,16 +8315,16 @@
         <v>28</v>
       </c>
       <c r="I81" t="s">
-        <v>661</v>
+        <v>737</v>
       </c>
       <c r="J81" t="s">
-        <v>662</v>
+        <v>738</v>
       </c>
       <c r="K81" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L81" t="s">
-        <v>681</v>
+        <v>760</v>
       </c>
       <c r="M81" t="s">
         <v>33</v>
@@ -8030,42 +8333,42 @@
         <v>28</v>
       </c>
       <c r="O81" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P81" t="s">
         <v>35</v>
       </c>
       <c r="Q81" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R81" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S81" t="s">
-        <v>665</v>
+        <v>741</v>
       </c>
       <c r="T81" t="s">
-        <v>666</v>
+        <v>742</v>
       </c>
       <c r="U81" t="s">
-        <v>667</v>
+        <v>743</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>21</v>
+        <v>761</v>
       </c>
       <c r="B82" t="s">
         <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D82" t="s">
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
@@ -8077,16 +8380,16 @@
         <v>28</v>
       </c>
       <c r="I82" t="s">
-        <v>682</v>
+        <v>762</v>
       </c>
       <c r="J82" t="s">
-        <v>683</v>
+        <v>763</v>
       </c>
       <c r="K82" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L82" t="s">
-        <v>684</v>
+        <v>764</v>
       </c>
       <c r="M82" t="s">
         <v>33</v>
@@ -8095,42 +8398,42 @@
         <v>28</v>
       </c>
       <c r="O82" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P82" t="s">
         <v>35</v>
       </c>
       <c r="Q82" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R82" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S82" t="s">
-        <v>685</v>
+        <v>765</v>
       </c>
       <c r="T82" t="s">
-        <v>686</v>
+        <v>766</v>
       </c>
       <c r="U82" t="s">
-        <v>687</v>
+        <v>767</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>768</v>
       </c>
       <c r="B83" t="s">
         <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>688</v>
+        <v>769</v>
       </c>
       <c r="D83" t="s">
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F83" t="s">
         <v>26</v>
@@ -8142,16 +8445,16 @@
         <v>28</v>
       </c>
       <c r="I83" t="s">
-        <v>676</v>
+        <v>754</v>
       </c>
       <c r="J83" t="s">
-        <v>662</v>
+        <v>738</v>
       </c>
       <c r="K83" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="L83" t="s">
-        <v>690</v>
+        <v>771</v>
       </c>
       <c r="M83" t="s">
         <v>33</v>
@@ -8160,42 +8463,42 @@
         <v>28</v>
       </c>
       <c r="O83" t="s">
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="P83" t="s">
-        <v>691</v>
+        <v>772</v>
       </c>
       <c r="Q83" t="s">
-        <v>692</v>
+        <v>773</v>
       </c>
       <c r="R83" t="s">
-        <v>693</v>
+        <v>774</v>
       </c>
       <c r="S83" t="s">
-        <v>679</v>
+        <v>757</v>
       </c>
       <c r="T83" t="s">
-        <v>666</v>
+        <v>742</v>
       </c>
       <c r="U83" t="s">
-        <v>680</v>
+        <v>758</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="B84" t="s">
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>694</v>
+        <v>776</v>
       </c>
       <c r="D84" t="s">
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="F84" t="s">
         <v>26</v>
@@ -8207,16 +8510,16 @@
         <v>28</v>
       </c>
       <c r="I84" t="s">
-        <v>695</v>
+        <v>777</v>
       </c>
       <c r="J84" t="s">
-        <v>696</v>
+        <v>778</v>
       </c>
       <c r="K84" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="L84" t="s">
-        <v>697</v>
+        <v>779</v>
       </c>
       <c r="M84" t="s">
         <v>33</v>
@@ -8225,42 +8528,42 @@
         <v>28</v>
       </c>
       <c r="O84" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="P84" t="s">
         <v>35</v>
       </c>
       <c r="Q84" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="R84" t="s">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="S84" t="s">
-        <v>698</v>
+        <v>780</v>
       </c>
       <c r="T84" t="s">
-        <v>699</v>
+        <v>781</v>
       </c>
       <c r="U84" t="s">
-        <v>700</v>
+        <v>782</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>783</v>
       </c>
       <c r="B85" t="s">
         <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>701</v>
+        <v>784</v>
       </c>
       <c r="D85" t="s">
         <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="F85" t="s">
         <v>26</v>
@@ -8272,16 +8575,16 @@
         <v>28</v>
       </c>
       <c r="I85" t="s">
-        <v>702</v>
+        <v>785</v>
       </c>
       <c r="J85" t="s">
-        <v>703</v>
+        <v>786</v>
       </c>
       <c r="K85" t="s">
-        <v>704</v>
+        <v>787</v>
       </c>
       <c r="L85" t="s">
-        <v>705</v>
+        <v>788</v>
       </c>
       <c r="M85" t="s">
         <v>33</v>
@@ -8290,42 +8593,42 @@
         <v>28</v>
       </c>
       <c r="O85" t="s">
-        <v>706</v>
+        <v>789</v>
       </c>
       <c r="P85" t="s">
         <v>35</v>
       </c>
       <c r="Q85" t="s">
-        <v>707</v>
+        <v>790</v>
       </c>
       <c r="R85" t="s">
-        <v>708</v>
+        <v>791</v>
       </c>
       <c r="S85" t="s">
-        <v>709</v>
+        <v>792</v>
       </c>
       <c r="T85" t="s">
-        <v>710</v>
+        <v>793</v>
       </c>
       <c r="U85" t="s">
-        <v>711</v>
+        <v>794</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>21</v>
+        <v>795</v>
       </c>
       <c r="B86" t="s">
         <v>22</v>
       </c>
       <c r="C86" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D86" t="s">
         <v>24</v>
       </c>
       <c r="E86" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F86" t="s">
         <v>26</v>
@@ -8337,16 +8640,16 @@
         <v>28</v>
       </c>
       <c r="I86" t="s">
-        <v>712</v>
+        <v>796</v>
       </c>
       <c r="J86" t="s">
-        <v>713</v>
+        <v>797</v>
       </c>
       <c r="K86" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L86" t="s">
-        <v>714</v>
+        <v>798</v>
       </c>
       <c r="M86" t="s">
         <v>33</v>
@@ -8355,42 +8658,42 @@
         <v>28</v>
       </c>
       <c r="O86" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P86" t="s">
         <v>35</v>
       </c>
       <c r="Q86" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R86" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S86" t="s">
-        <v>715</v>
+        <v>799</v>
       </c>
       <c r="T86" t="s">
-        <v>716</v>
+        <v>800</v>
       </c>
       <c r="U86" t="s">
-        <v>717</v>
+        <v>801</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>21</v>
+        <v>802</v>
       </c>
       <c r="B87" t="s">
         <v>22</v>
       </c>
       <c r="C87" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D87" t="s">
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F87" t="s">
         <v>26</v>
@@ -8402,16 +8705,16 @@
         <v>28</v>
       </c>
       <c r="I87" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J87" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="K87" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="L87" t="s">
-        <v>718</v>
+        <v>803</v>
       </c>
       <c r="M87" t="s">
         <v>33</v>
@@ -8420,42 +8723,42 @@
         <v>28</v>
       </c>
       <c r="O87" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="P87" t="s">
         <v>35</v>
       </c>
       <c r="Q87" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="R87" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="S87" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="T87" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="U87" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>21</v>
+        <v>804</v>
       </c>
       <c r="B88" t="s">
         <v>22</v>
       </c>
       <c r="C88" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D88" t="s">
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F88" t="s">
         <v>26</v>
@@ -8467,16 +8770,16 @@
         <v>28</v>
       </c>
       <c r="I88" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="J88" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="K88" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="L88" t="s">
-        <v>719</v>
+        <v>805</v>
       </c>
       <c r="M88" t="s">
         <v>33</v>
@@ -8485,30 +8788,30 @@
         <v>28</v>
       </c>
       <c r="O88" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="P88" t="s">
         <v>35</v>
       </c>
       <c r="Q88" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="R88" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="S88" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="T88" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="U88" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>21</v>
+        <v>806</v>
       </c>
       <c r="B89" t="s">
         <v>22</v>
@@ -8520,7 +8823,7 @@
         <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F89" t="s">
         <v>26</v>
@@ -8532,16 +8835,16 @@
         <v>28</v>
       </c>
       <c r="I89" t="s">
-        <v>720</v>
+        <v>807</v>
       </c>
       <c r="J89" t="s">
-        <v>721</v>
+        <v>808</v>
       </c>
       <c r="K89" t="s">
-        <v>640</v>
+        <v>713</v>
       </c>
       <c r="L89" t="s">
-        <v>722</v>
+        <v>809</v>
       </c>
       <c r="M89" t="s">
         <v>33</v>
@@ -8550,42 +8853,42 @@
         <v>28</v>
       </c>
       <c r="O89" t="s">
-        <v>642</v>
+        <v>715</v>
       </c>
       <c r="P89" t="s">
         <v>35</v>
       </c>
       <c r="Q89" t="s">
-        <v>643</v>
+        <v>716</v>
       </c>
       <c r="R89" t="s">
-        <v>644</v>
+        <v>717</v>
       </c>
       <c r="S89" t="s">
-        <v>723</v>
+        <v>810</v>
       </c>
       <c r="T89" t="s">
-        <v>724</v>
+        <v>811</v>
       </c>
       <c r="U89" t="s">
-        <v>725</v>
+        <v>812</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>21</v>
+        <v>813</v>
       </c>
       <c r="B90" t="s">
         <v>22</v>
       </c>
       <c r="C90" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D90" t="s">
         <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F90" t="s">
         <v>26</v>
@@ -8597,16 +8900,16 @@
         <v>28</v>
       </c>
       <c r="I90" t="s">
-        <v>726</v>
+        <v>814</v>
       </c>
       <c r="J90" t="s">
-        <v>727</v>
+        <v>815</v>
       </c>
       <c r="K90" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L90" t="s">
-        <v>728</v>
+        <v>816</v>
       </c>
       <c r="M90" t="s">
         <v>33</v>
@@ -8615,42 +8918,42 @@
         <v>28</v>
       </c>
       <c r="O90" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P90" t="s">
         <v>35</v>
       </c>
       <c r="Q90" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R90" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S90" t="s">
-        <v>729</v>
+        <v>817</v>
       </c>
       <c r="T90" t="s">
-        <v>730</v>
+        <v>818</v>
       </c>
       <c r="U90" t="s">
-        <v>731</v>
+        <v>819</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>21</v>
+        <v>820</v>
       </c>
       <c r="B91" t="s">
         <v>22</v>
       </c>
       <c r="C91" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D91" t="s">
         <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F91" t="s">
         <v>26</v>
@@ -8662,16 +8965,16 @@
         <v>28</v>
       </c>
       <c r="I91" t="s">
-        <v>732</v>
+        <v>821</v>
       </c>
       <c r="J91" t="s">
-        <v>733</v>
+        <v>822</v>
       </c>
       <c r="K91" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L91" t="s">
-        <v>734</v>
+        <v>823</v>
       </c>
       <c r="M91" t="s">
         <v>33</v>
@@ -8680,42 +8983,42 @@
         <v>28</v>
       </c>
       <c r="O91" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P91" t="s">
         <v>35</v>
       </c>
       <c r="Q91" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R91" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S91" t="s">
-        <v>735</v>
+        <v>824</v>
       </c>
       <c r="T91" t="s">
-        <v>736</v>
+        <v>825</v>
       </c>
       <c r="U91" t="s">
-        <v>737</v>
+        <v>826</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>21</v>
+        <v>827</v>
       </c>
       <c r="B92" t="s">
         <v>22</v>
       </c>
       <c r="C92" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D92" t="s">
         <v>24</v>
       </c>
       <c r="E92" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F92" t="s">
         <v>26</v>
@@ -8727,16 +9030,16 @@
         <v>28</v>
       </c>
       <c r="I92" t="s">
-        <v>738</v>
+        <v>828</v>
       </c>
       <c r="J92" t="s">
-        <v>739</v>
+        <v>829</v>
       </c>
       <c r="K92" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L92" t="s">
-        <v>740</v>
+        <v>830</v>
       </c>
       <c r="M92" t="s">
         <v>33</v>
@@ -8745,30 +9048,30 @@
         <v>28</v>
       </c>
       <c r="O92" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P92" t="s">
         <v>35</v>
       </c>
       <c r="Q92" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R92" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S92" t="s">
-        <v>741</v>
+        <v>831</v>
       </c>
       <c r="T92" t="s">
-        <v>742</v>
+        <v>832</v>
       </c>
       <c r="U92" t="s">
-        <v>743</v>
+        <v>833</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>21</v>
+        <v>834</v>
       </c>
       <c r="B93" t="s">
         <v>22</v>
@@ -8780,7 +9083,7 @@
         <v>24</v>
       </c>
       <c r="E93" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F93" t="s">
         <v>35</v>
@@ -8792,16 +9095,16 @@
         <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>744</v>
+        <v>835</v>
       </c>
       <c r="J93" t="s">
-        <v>745</v>
+        <v>836</v>
       </c>
       <c r="K93" t="s">
-        <v>746</v>
+        <v>837</v>
       </c>
       <c r="L93" t="s">
-        <v>747</v>
+        <v>838</v>
       </c>
       <c r="M93" t="s">
         <v>33</v>
@@ -8810,42 +9113,42 @@
         <v>28</v>
       </c>
       <c r="O93" t="s">
-        <v>748</v>
+        <v>839</v>
       </c>
       <c r="P93" t="s">
         <v>35</v>
       </c>
       <c r="Q93" t="s">
-        <v>749</v>
+        <v>840</v>
       </c>
       <c r="R93" t="s">
-        <v>750</v>
+        <v>841</v>
       </c>
       <c r="S93" t="s">
-        <v>751</v>
+        <v>842</v>
       </c>
       <c r="T93" t="s">
-        <v>752</v>
+        <v>843</v>
       </c>
       <c r="U93" t="s">
-        <v>753</v>
+        <v>844</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="B94" t="s">
         <v>22</v>
       </c>
       <c r="C94" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D94" t="s">
         <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F94" t="s">
         <v>26</v>
@@ -8857,16 +9160,16 @@
         <v>28</v>
       </c>
       <c r="I94" t="s">
-        <v>754</v>
+        <v>846</v>
       </c>
       <c r="J94" t="s">
-        <v>755</v>
+        <v>847</v>
       </c>
       <c r="K94" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L94" t="s">
-        <v>756</v>
+        <v>848</v>
       </c>
       <c r="M94" t="s">
         <v>33</v>
@@ -8875,42 +9178,42 @@
         <v>28</v>
       </c>
       <c r="O94" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P94" t="s">
         <v>35</v>
       </c>
       <c r="Q94" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R94" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S94" t="s">
-        <v>757</v>
+        <v>849</v>
       </c>
       <c r="T94" t="s">
-        <v>758</v>
+        <v>850</v>
       </c>
       <c r="U94" t="s">
-        <v>759</v>
+        <v>851</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>21</v>
+        <v>852</v>
       </c>
       <c r="B95" t="s">
         <v>22</v>
       </c>
       <c r="C95" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D95" t="s">
         <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F95" t="s">
         <v>26</v>
@@ -8922,16 +9225,16 @@
         <v>28</v>
       </c>
       <c r="I95" t="s">
-        <v>760</v>
+        <v>853</v>
       </c>
       <c r="J95" t="s">
-        <v>761</v>
+        <v>854</v>
       </c>
       <c r="K95" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L95" t="s">
-        <v>762</v>
+        <v>855</v>
       </c>
       <c r="M95" t="s">
         <v>33</v>
@@ -8940,42 +9243,42 @@
         <v>28</v>
       </c>
       <c r="O95" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P95" t="s">
         <v>35</v>
       </c>
       <c r="Q95" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R95" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S95" t="s">
-        <v>763</v>
+        <v>856</v>
       </c>
       <c r="T95" t="s">
-        <v>764</v>
+        <v>857</v>
       </c>
       <c r="U95" t="s">
-        <v>765</v>
+        <v>858</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>21</v>
+        <v>859</v>
       </c>
       <c r="B96" t="s">
         <v>22</v>
       </c>
       <c r="C96" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D96" t="s">
         <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F96" t="s">
         <v>26</v>
@@ -8987,16 +9290,16 @@
         <v>28</v>
       </c>
       <c r="I96" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J96" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K96" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L96" t="s">
-        <v>766</v>
+        <v>860</v>
       </c>
       <c r="M96" t="s">
         <v>33</v>
@@ -9005,42 +9308,42 @@
         <v>28</v>
       </c>
       <c r="O96" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P96" t="s">
         <v>35</v>
       </c>
       <c r="Q96" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R96" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="S96" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="T96" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="U96" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>21</v>
+        <v>861</v>
       </c>
       <c r="B97" t="s">
         <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D97" t="s">
         <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F97" t="s">
         <v>26</v>
@@ -9052,16 +9355,16 @@
         <v>28</v>
       </c>
       <c r="I97" t="s">
-        <v>767</v>
+        <v>862</v>
       </c>
       <c r="J97" t="s">
-        <v>768</v>
+        <v>863</v>
       </c>
       <c r="K97" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L97" t="s">
-        <v>769</v>
+        <v>864</v>
       </c>
       <c r="M97" t="s">
         <v>33</v>
@@ -9070,30 +9373,30 @@
         <v>28</v>
       </c>
       <c r="O97" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P97" t="s">
         <v>35</v>
       </c>
       <c r="Q97" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R97" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S97" t="s">
-        <v>770</v>
+        <v>865</v>
       </c>
       <c r="T97" t="s">
-        <v>771</v>
+        <v>866</v>
       </c>
       <c r="U97" t="s">
-        <v>772</v>
+        <v>867</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>21</v>
+        <v>868</v>
       </c>
       <c r="B98" t="s">
         <v>22</v>
@@ -9105,7 +9408,7 @@
         <v>24</v>
       </c>
       <c r="E98" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F98" t="s">
         <v>26</v>
@@ -9117,16 +9420,16 @@
         <v>28</v>
       </c>
       <c r="I98" t="s">
-        <v>773</v>
+        <v>869</v>
       </c>
       <c r="J98" t="s">
-        <v>774</v>
+        <v>870</v>
       </c>
       <c r="K98" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L98" t="s">
-        <v>775</v>
+        <v>871</v>
       </c>
       <c r="M98" t="s">
         <v>33</v>
@@ -9135,42 +9438,42 @@
         <v>28</v>
       </c>
       <c r="O98" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P98" t="s">
         <v>35</v>
       </c>
       <c r="Q98" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R98" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="S98" t="s">
-        <v>776</v>
+        <v>872</v>
       </c>
       <c r="T98" t="s">
-        <v>777</v>
+        <v>873</v>
       </c>
       <c r="U98" t="s">
-        <v>778</v>
+        <v>874</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>21</v>
+        <v>875</v>
       </c>
       <c r="B99" t="s">
         <v>22</v>
       </c>
       <c r="C99" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="D99" t="s">
         <v>24</v>
       </c>
       <c r="E99" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F99" t="s">
         <v>26</v>
@@ -9182,16 +9485,16 @@
         <v>28</v>
       </c>
       <c r="I99" t="s">
-        <v>779</v>
+        <v>876</v>
       </c>
       <c r="J99" t="s">
-        <v>780</v>
+        <v>877</v>
       </c>
       <c r="K99" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L99" t="s">
-        <v>781</v>
+        <v>878</v>
       </c>
       <c r="M99" t="s">
         <v>33</v>
@@ -9200,42 +9503,42 @@
         <v>28</v>
       </c>
       <c r="O99" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P99" t="s">
         <v>35</v>
       </c>
       <c r="Q99" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R99" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S99" t="s">
-        <v>782</v>
+        <v>879</v>
       </c>
       <c r="T99" t="s">
-        <v>783</v>
+        <v>880</v>
       </c>
       <c r="U99" t="s">
-        <v>784</v>
+        <v>881</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>21</v>
+        <v>882</v>
       </c>
       <c r="B100" t="s">
         <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D100" t="s">
         <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="F100" t="s">
         <v>26</v>
@@ -9247,16 +9550,16 @@
         <v>28</v>
       </c>
       <c r="I100" t="s">
-        <v>785</v>
+        <v>883</v>
       </c>
       <c r="J100" t="s">
-        <v>786</v>
+        <v>884</v>
       </c>
       <c r="K100" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="L100" t="s">
-        <v>787</v>
+        <v>885</v>
       </c>
       <c r="M100" t="s">
         <v>33</v>
@@ -9265,42 +9568,42 @@
         <v>28</v>
       </c>
       <c r="O100" t="s">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P100" t="s">
         <v>35</v>
       </c>
       <c r="Q100" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="R100" t="s">
-        <v>463</v>
+        <v>508</v>
       </c>
       <c r="S100" t="s">
-        <v>788</v>
+        <v>886</v>
       </c>
       <c r="T100" t="s">
-        <v>789</v>
+        <v>887</v>
       </c>
       <c r="U100" t="s">
-        <v>790</v>
+        <v>888</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>21</v>
+        <v>889</v>
       </c>
       <c r="B101" t="s">
         <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>791</v>
+        <v>890</v>
       </c>
       <c r="D101" t="s">
         <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F101" t="s">
         <v>26</v>
@@ -9312,16 +9615,16 @@
         <v>28</v>
       </c>
       <c r="I101" t="s">
-        <v>792</v>
+        <v>891</v>
       </c>
       <c r="J101" t="s">
-        <v>793</v>
+        <v>892</v>
       </c>
       <c r="K101" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="L101" t="s">
-        <v>794</v>
+        <v>893</v>
       </c>
       <c r="M101" t="s">
         <v>33</v>
@@ -9330,36 +9633,36 @@
         <v>28</v>
       </c>
       <c r="O101" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="P101" t="s">
         <v>35</v>
       </c>
       <c r="Q101" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="R101" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="S101" t="s">
-        <v>795</v>
+        <v>894</v>
       </c>
       <c r="T101" t="s">
-        <v>796</v>
+        <v>895</v>
       </c>
       <c r="U101" t="s">
-        <v>797</v>
+        <v>896</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>21</v>
+        <v>897</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>798</v>
+        <v>898</v>
       </c>
       <c r="D102" t="s">
         <v>24</v>
@@ -9377,16 +9680,16 @@
         <v>28</v>
       </c>
       <c r="I102" t="s">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="J102" t="s">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K102" t="s">
         <v>31</v>
       </c>
       <c r="L102" t="s">
-        <v>801</v>
+        <v>901</v>
       </c>
       <c r="M102" t="s">
         <v>33</v>
@@ -9407,30 +9710,30 @@
         <v>37</v>
       </c>
       <c r="S102" t="s">
-        <v>802</v>
+        <v>902</v>
       </c>
       <c r="T102" t="s">
-        <v>803</v>
+        <v>903</v>
       </c>
       <c r="U102" t="s">
-        <v>804</v>
+        <v>904</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>21</v>
+        <v>905</v>
       </c>
       <c r="B103" t="s">
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>805</v>
+        <v>906</v>
       </c>
       <c r="D103" t="s">
         <v>24</v>
       </c>
       <c r="E103" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F103" t="s">
         <v>26</v>
@@ -9442,16 +9745,16 @@
         <v>28</v>
       </c>
       <c r="I103" t="s">
-        <v>806</v>
+        <v>907</v>
       </c>
       <c r="J103" t="s">
-        <v>807</v>
+        <v>908</v>
       </c>
       <c r="K103" t="s">
-        <v>808</v>
+        <v>909</v>
       </c>
       <c r="L103" t="s">
-        <v>809</v>
+        <v>910</v>
       </c>
       <c r="M103" t="s">
         <v>33</v>
@@ -9460,42 +9763,42 @@
         <v>28</v>
       </c>
       <c r="O103" t="s">
-        <v>808</v>
+        <v>909</v>
       </c>
       <c r="P103" t="s">
-        <v>810</v>
+        <v>911</v>
       </c>
       <c r="Q103" t="s">
-        <v>811</v>
+        <v>912</v>
       </c>
       <c r="R103" t="s">
-        <v>812</v>
+        <v>913</v>
       </c>
       <c r="S103" t="s">
-        <v>813</v>
+        <v>914</v>
       </c>
       <c r="T103" t="s">
-        <v>814</v>
+        <v>915</v>
       </c>
       <c r="U103" t="s">
-        <v>815</v>
+        <v>916</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="B104" t="s">
         <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="D104" t="s">
         <v>24</v>
       </c>
       <c r="E104" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F104" t="s">
         <v>26</v>
@@ -9507,16 +9810,16 @@
         <v>28</v>
       </c>
       <c r="I104" t="s">
-        <v>816</v>
+        <v>917</v>
       </c>
       <c r="J104" t="s">
-        <v>817</v>
+        <v>918</v>
       </c>
       <c r="K104" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="L104" t="s">
-        <v>818</v>
+        <v>919</v>
       </c>
       <c r="M104" t="s">
         <v>33</v>
@@ -9525,25 +9828,25 @@
         <v>28</v>
       </c>
       <c r="O104" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="P104" t="s">
-        <v>819</v>
+        <v>920</v>
       </c>
       <c r="Q104" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="R104" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="S104" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="T104" t="s">
-        <v>820</v>
+        <v>921</v>
       </c>
       <c r="U104" t="s">
-        <v>821</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>
